--- a/Mapa - Zelar.xlsx
+++ b/Mapa - Zelar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aguinir.junior\Desktop\Gestão\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1AF8BE-8553-4253-B8D0-31C6535772AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E35097-75DD-468C-A8AE-E2F8B16AB135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4278" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4343" uniqueCount="1940">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -5852,6 +5852,15 @@
   </si>
   <si>
     <t>JOÃO PINHEIRO</t>
+  </si>
+  <si>
+    <t>SETEMBRO/26</t>
+  </si>
+  <si>
+    <t>NÃO IDENTIFICADO</t>
+  </si>
+  <si>
+    <t>OPERAÇÃO FULL</t>
   </si>
 </sst>
 </file>
@@ -5893,10 +5902,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6163,7 +6173,8 @@
   <cols>
     <col min="1" max="1" width="41.33203125" customWidth="1"/>
     <col min="2" max="2" width="41.5546875" customWidth="1"/>
-    <col min="3" max="5" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="3" customWidth="1"/>
+    <col min="4" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="29.5546875" customWidth="1"/>
     <col min="7" max="7" width="33.77734375" customWidth="1"/>
     <col min="8" max="8" width="8.33203125" customWidth="1"/>
@@ -6179,7 +6190,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -6214,7 +6225,7 @@
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
@@ -6249,7 +6260,7 @@
       <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D3" t="s">
@@ -6284,7 +6295,7 @@
       <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D4" t="s">
@@ -6319,7 +6330,7 @@
       <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D5" t="s">
@@ -6354,7 +6365,7 @@
       <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
@@ -6389,7 +6400,7 @@
       <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D7" t="s">
@@ -6424,8 +6435,11 @@
       <c r="B8" t="s">
         <v>52</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>507</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" t="s">
@@ -6448,7 +6462,7 @@
       <c r="B9" t="s">
         <v>56</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D9" t="s">
@@ -6483,7 +6497,7 @@
       <c r="B10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D10" t="s">
@@ -6518,7 +6532,7 @@
       <c r="B11" t="s">
         <v>69</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D11" t="s">
@@ -6553,7 +6567,7 @@
       <c r="B12" t="s">
         <v>73</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D12" t="s">
@@ -6588,7 +6602,7 @@
       <c r="B13" t="s">
         <v>78</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D13" t="s">
@@ -6623,8 +6637,11 @@
       <c r="B14" t="s">
         <v>84</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>706</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" t="s">
@@ -6647,7 +6664,7 @@
       <c r="B15" t="s">
         <v>88</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D15" t="s">
@@ -6682,7 +6699,7 @@
       <c r="B16" t="s">
         <v>92</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D16" t="s">
@@ -6717,7 +6734,7 @@
       <c r="B17" t="s">
         <v>98</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D17" t="s">
@@ -6752,8 +6769,11 @@
       <c r="B18" t="s">
         <v>103</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>177</v>
+      </c>
+      <c r="D18" t="s">
+        <v>58</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" t="s">
@@ -6776,7 +6796,7 @@
       <c r="B19" t="s">
         <v>108</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>109</v>
       </c>
       <c r="D19" t="s">
@@ -6811,7 +6831,7 @@
       <c r="B20" t="s">
         <v>113</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D20" t="s">
@@ -6846,7 +6866,7 @@
       <c r="B21" t="s">
         <v>117</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D21" t="s">
@@ -6881,7 +6901,7 @@
       <c r="B22" t="s">
         <v>123</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
@@ -6916,7 +6936,7 @@
       <c r="B23" t="s">
         <v>128</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D23" t="s">
@@ -6951,7 +6971,7 @@
       <c r="B24" t="s">
         <v>132</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D24" t="s">
@@ -6986,7 +7006,7 @@
       <c r="B25" t="s">
         <v>135</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D25" t="s">
@@ -7021,7 +7041,7 @@
       <c r="B26" t="s">
         <v>139</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D26" t="s">
@@ -7056,7 +7076,7 @@
       <c r="B27" t="s">
         <v>145</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D27" t="s">
@@ -7091,7 +7111,7 @@
       <c r="B28" t="s">
         <v>149</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D28" t="s">
@@ -7126,7 +7146,7 @@
       <c r="B29" t="s">
         <v>152</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D29" t="s">
@@ -7161,7 +7181,7 @@
       <c r="B30" t="s">
         <v>155</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D30" t="s">
@@ -7196,7 +7216,7 @@
       <c r="B31" t="s">
         <v>159</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D31" t="s">
@@ -7231,8 +7251,11 @@
       <c r="B32" t="s">
         <v>164</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>367</v>
+      </c>
+      <c r="D32" t="s">
+        <v>31</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" t="s">
@@ -7255,8 +7278,11 @@
       <c r="B33" t="s">
         <v>167</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>136</v>
+      </c>
+      <c r="D33" t="s">
+        <v>58</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s">
@@ -7279,7 +7305,7 @@
       <c r="B34" t="s">
         <v>170</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="3" t="s">
         <v>171</v>
       </c>
       <c r="D34" t="s">
@@ -7314,7 +7340,7 @@
       <c r="B35" t="s">
         <v>176</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D35" t="s">
@@ -7349,7 +7375,7 @@
       <c r="B36" t="s">
         <v>181</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>182</v>
       </c>
       <c r="D36" t="s">
@@ -7384,7 +7410,7 @@
       <c r="B37" t="s">
         <v>186</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D37" t="s">
@@ -7419,7 +7445,7 @@
       <c r="B38" t="s">
         <v>191</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>192</v>
       </c>
       <c r="D38" t="s">
@@ -7454,7 +7480,7 @@
       <c r="B39" t="s">
         <v>195</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>196</v>
       </c>
       <c r="D39" t="s">
@@ -7489,7 +7515,7 @@
       <c r="B40" t="s">
         <v>200</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>196</v>
       </c>
       <c r="D40" t="s">
@@ -7524,7 +7550,7 @@
       <c r="B41" t="s">
         <v>204</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>196</v>
       </c>
       <c r="D41" t="s">
@@ -7559,7 +7585,7 @@
       <c r="B42" t="s">
         <v>208</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D42" t="s">
@@ -7594,7 +7620,7 @@
       <c r="B43" t="s">
         <v>212</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D43" t="s">
@@ -7629,7 +7655,7 @@
       <c r="B44" t="s">
         <v>216</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
         <v>217</v>
       </c>
       <c r="D44" t="s">
@@ -7664,6 +7690,12 @@
       <c r="B45" t="s">
         <v>220</v>
       </c>
+      <c r="C45" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>1938</v>
+      </c>
       <c r="E45" t="s">
         <v>15</v>
       </c>
@@ -7693,8 +7725,8 @@
       <c r="B46" t="s">
         <v>223</v>
       </c>
-      <c r="C46">
-        <v>45239.125</v>
+      <c r="C46" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="D46" t="s">
         <v>58</v>
@@ -7728,6 +7760,12 @@
       <c r="B47" t="s">
         <v>226</v>
       </c>
+      <c r="C47" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1938</v>
+      </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
@@ -7757,7 +7795,7 @@
       <c r="B48" t="s">
         <v>229</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D48" t="s">
@@ -7792,7 +7830,7 @@
       <c r="B49" t="s">
         <v>233</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D49" t="s">
@@ -7827,7 +7865,7 @@
       <c r="B50" t="s">
         <v>236</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D50" t="s">
@@ -7862,8 +7900,8 @@
       <c r="B51" t="s">
         <v>240</v>
       </c>
-      <c r="C51">
-        <v>45534.125</v>
+      <c r="C51" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="D51" t="s">
         <v>58</v>
@@ -7897,6 +7935,12 @@
       <c r="B52" t="s">
         <v>243</v>
       </c>
+      <c r="C52" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>1938</v>
+      </c>
       <c r="E52" t="s">
         <v>15</v>
       </c>
@@ -7926,8 +7970,11 @@
       <c r="B53" t="s">
         <v>246</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="3" t="s">
         <v>848</v>
+      </c>
+      <c r="D53" t="s">
+        <v>58</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s">
@@ -7950,6 +7997,12 @@
       <c r="B54" t="s">
         <v>250</v>
       </c>
+      <c r="C54" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>1938</v>
+      </c>
       <c r="E54" t="s">
         <v>15</v>
       </c>
@@ -7979,7 +8032,7 @@
       <c r="B55" t="s">
         <v>253</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D55" t="s">
@@ -8014,8 +8067,8 @@
       <c r="B56" t="s">
         <v>256</v>
       </c>
-      <c r="C56">
-        <v>45295.125</v>
+      <c r="C56" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="D56" t="s">
         <v>30</v>
@@ -8049,6 +8102,12 @@
       <c r="B57" t="s">
         <v>259</v>
       </c>
+      <c r="C57" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>1938</v>
+      </c>
       <c r="E57" t="s">
         <v>15</v>
       </c>
@@ -8078,7 +8137,7 @@
       <c r="B58" t="s">
         <v>262</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D58" t="s">
@@ -8113,8 +8172,8 @@
       <c r="B59" t="s">
         <v>265</v>
       </c>
-      <c r="C59">
-        <v>45350.125</v>
+      <c r="C59" s="3" t="s">
+        <v>848</v>
       </c>
       <c r="D59" t="s">
         <v>58</v>
@@ -8148,8 +8207,11 @@
       <c r="B60" t="s">
         <v>269</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="3" t="s">
         <v>47</v>
+      </c>
+      <c r="D60" t="s">
+        <v>58</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s">
@@ -8172,7 +8234,7 @@
       <c r="B61" t="s">
         <v>273</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D61" t="s">
@@ -8207,7 +8269,7 @@
       <c r="B62" t="s">
         <v>279</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D62" t="s">
@@ -8242,7 +8304,7 @@
       <c r="B63" t="s">
         <v>281</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D63" t="s">
@@ -8277,7 +8339,7 @@
       <c r="B64" t="s">
         <v>285</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D64" t="s">
@@ -8312,7 +8374,7 @@
       <c r="B65" t="s">
         <v>288</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D65" t="s">
@@ -8347,7 +8409,7 @@
       <c r="B66" t="s">
         <v>290</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D66" t="s">
@@ -8382,7 +8444,7 @@
       <c r="B67" t="s">
         <v>294</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D67" t="s">
@@ -8417,7 +8479,7 @@
       <c r="B68" t="s">
         <v>297</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D68" t="s">
@@ -8452,7 +8514,7 @@
       <c r="B69" t="s">
         <v>300</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D69" t="s">
@@ -8487,7 +8549,7 @@
       <c r="B70" t="s">
         <v>303</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D70" t="s">
@@ -8522,7 +8584,7 @@
       <c r="B71" t="s">
         <v>305</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D71" t="s">
@@ -8557,7 +8619,7 @@
       <c r="B72" t="s">
         <v>308</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D72" t="s">
@@ -8592,7 +8654,7 @@
       <c r="B73" t="s">
         <v>311</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D73" t="s">
@@ -8627,7 +8689,7 @@
       <c r="B74" t="s">
         <v>316</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D74" t="s">
@@ -8662,7 +8724,7 @@
       <c r="B75" t="s">
         <v>319</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D75" t="s">
@@ -8697,7 +8759,7 @@
       <c r="B76" t="s">
         <v>323</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="3" t="s">
         <v>324</v>
       </c>
       <c r="D76" t="s">
@@ -8732,7 +8794,7 @@
       <c r="B77" t="s">
         <v>328</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D77" t="s">
@@ -8767,8 +8829,11 @@
       <c r="B78" t="s">
         <v>331</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="3" t="s">
         <v>1133</v>
+      </c>
+      <c r="D78" t="s">
+        <v>58</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" t="s">
@@ -8791,7 +8856,7 @@
       <c r="B79" t="s">
         <v>335</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D79" t="s">
@@ -8826,7 +8891,7 @@
       <c r="B80" t="s">
         <v>338</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D80" t="s">
@@ -8861,7 +8926,7 @@
       <c r="B81" t="s">
         <v>341</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D81" t="s">
@@ -8896,7 +8961,7 @@
       <c r="B82" t="s">
         <v>346</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D82" t="s">
@@ -8931,7 +8996,7 @@
       <c r="B83" t="s">
         <v>349</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="3" t="s">
         <v>350</v>
       </c>
       <c r="D83" t="s">
@@ -8966,8 +9031,11 @@
       <c r="B84" t="s">
         <v>353</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="3" t="s">
         <v>1929</v>
+      </c>
+      <c r="D84" t="s">
+        <v>31</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" t="s">
@@ -8990,7 +9058,7 @@
       <c r="B85" t="s">
         <v>356</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D85" t="s">
@@ -9025,7 +9093,7 @@
       <c r="B86" t="s">
         <v>360</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D86" t="s">
@@ -9060,7 +9128,7 @@
       <c r="B87" t="s">
         <v>365</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="3" t="s">
         <v>366</v>
       </c>
       <c r="D87" t="s">
@@ -9095,7 +9163,7 @@
       <c r="B88" t="s">
         <v>373</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D88" t="s">
@@ -9130,8 +9198,11 @@
       <c r="B89" t="s">
         <v>377</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="3" t="s">
         <v>387</v>
+      </c>
+      <c r="D89" t="s">
+        <v>58</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" t="s">
@@ -9154,7 +9225,7 @@
       <c r="B90" t="s">
         <v>380</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="3" t="s">
         <v>381</v>
       </c>
       <c r="D90" t="s">
@@ -9189,7 +9260,7 @@
       <c r="B91" t="s">
         <v>386</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="3" t="s">
         <v>387</v>
       </c>
       <c r="D91" t="s">
@@ -9224,7 +9295,7 @@
       <c r="B92" t="s">
         <v>391</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="3" t="s">
         <v>392</v>
       </c>
       <c r="D92" t="s">
@@ -9259,7 +9330,7 @@
       <c r="B93" t="s">
         <v>396</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D93" t="s">
@@ -9294,7 +9365,7 @@
       <c r="B94" t="s">
         <v>401</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D94" t="s">
@@ -9329,7 +9400,7 @@
       <c r="B95" t="s">
         <v>405</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="3" t="s">
         <v>171</v>
       </c>
       <c r="D95" t="s">
@@ -9364,7 +9435,7 @@
       <c r="B96" t="s">
         <v>408</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="3" t="s">
         <v>409</v>
       </c>
       <c r="D96" t="s">
@@ -9399,7 +9470,7 @@
       <c r="B97" t="s">
         <v>412</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="3" t="s">
         <v>171</v>
       </c>
       <c r="D97" t="s">
@@ -9434,7 +9505,7 @@
       <c r="B98" t="s">
         <v>414</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D98" t="s">
@@ -9469,8 +9540,11 @@
       <c r="B99" t="s">
         <v>417</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="D99" t="s">
+        <v>31</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" t="s">
@@ -9493,8 +9567,11 @@
       <c r="B100" t="s">
         <v>421</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="3" t="s">
         <v>38</v>
+      </c>
+      <c r="D100" t="s">
+        <v>58</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s">
@@ -9517,7 +9594,7 @@
       <c r="B101" t="s">
         <v>424</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D101" t="s">
@@ -9552,7 +9629,7 @@
       <c r="B102" t="s">
         <v>428</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D102" t="s">
@@ -9587,7 +9664,7 @@
       <c r="B103" t="s">
         <v>431</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D103" t="s">
@@ -9622,7 +9699,7 @@
       <c r="B104" t="s">
         <v>434</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D104" t="s">
@@ -9657,7 +9734,7 @@
       <c r="B105" t="s">
         <v>437</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D105" t="s">
@@ -9692,7 +9769,7 @@
       <c r="B106" t="s">
         <v>440</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D106" t="s">
@@ -9727,7 +9804,7 @@
       <c r="B107" t="s">
         <v>443</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D107" t="s">
@@ -9762,7 +9839,7 @@
       <c r="B108" t="s">
         <v>446</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D108" t="s">
@@ -9797,7 +9874,7 @@
       <c r="B109" t="s">
         <v>449</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D109" t="s">
@@ -9832,7 +9909,7 @@
       <c r="B110" t="s">
         <v>452</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D110" t="s">
@@ -9867,7 +9944,7 @@
       <c r="B111" t="s">
         <v>455</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D111" t="s">
@@ -9902,7 +9979,7 @@
       <c r="B112" t="s">
         <v>458</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D112" t="s">
@@ -9937,7 +10014,7 @@
       <c r="B113" t="s">
         <v>461</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D113" t="s">
@@ -9972,7 +10049,7 @@
       <c r="B114" t="s">
         <v>464</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D114" t="s">
@@ -10007,7 +10084,7 @@
       <c r="B115" t="s">
         <v>467</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D115" t="s">
@@ -10042,7 +10119,7 @@
       <c r="B116" t="s">
         <v>470</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D116" t="s">
@@ -10077,7 +10154,7 @@
       <c r="B117" t="s">
         <v>473</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D117" t="s">
@@ -10112,7 +10189,7 @@
       <c r="B118" t="s">
         <v>475</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D118" t="s">
@@ -10147,7 +10224,7 @@
       <c r="B119" t="s">
         <v>478</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D119" t="s">
@@ -10182,7 +10259,7 @@
       <c r="B120" t="s">
         <v>483</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="3" t="s">
         <v>484</v>
       </c>
       <c r="D120" t="s">
@@ -10217,7 +10294,7 @@
       <c r="B121" t="s">
         <v>487</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D121" t="s">
@@ -10252,7 +10329,7 @@
       <c r="B122" t="s">
         <v>492</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D122" t="s">
@@ -10287,8 +10364,11 @@
       <c r="B123" t="s">
         <v>498</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="3" t="s">
         <v>503</v>
+      </c>
+      <c r="D123" t="s">
+        <v>58</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" t="s">
@@ -10311,7 +10391,7 @@
       <c r="B124" t="s">
         <v>502</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="3" t="s">
         <v>503</v>
       </c>
       <c r="D124" t="s">
@@ -10346,7 +10426,7 @@
       <c r="B125" t="s">
         <v>506</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D125" t="s">
@@ -10381,8 +10461,11 @@
       <c r="B126" t="s">
         <v>512</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="3" t="s">
         <v>1929</v>
+      </c>
+      <c r="D126" t="s">
+        <v>31</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" t="s">
@@ -10405,8 +10488,11 @@
       <c r="B127" t="s">
         <v>516</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="3" t="s">
         <v>1929</v>
+      </c>
+      <c r="D127" t="s">
+        <v>31</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" t="s">
@@ -10429,7 +10515,7 @@
       <c r="B128" t="s">
         <v>520</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="3" t="s">
         <v>503</v>
       </c>
       <c r="D128" t="s">
@@ -10464,7 +10550,7 @@
       <c r="B129" t="s">
         <v>523</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D129" t="s">
@@ -10499,7 +10585,7 @@
       <c r="B130" t="s">
         <v>526</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D130" t="s">
@@ -10534,8 +10620,11 @@
       <c r="B131" t="s">
         <v>529</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="3" t="s">
         <v>848</v>
+      </c>
+      <c r="D131" t="s">
+        <v>58</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" t="s">
@@ -10558,8 +10647,11 @@
       <c r="B132" t="s">
         <v>532</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="3" t="s">
         <v>188</v>
+      </c>
+      <c r="D132" t="s">
+        <v>31</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" t="s">
@@ -10582,7 +10674,7 @@
       <c r="B133" t="s">
         <v>537</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D133" t="s">
@@ -10617,7 +10709,7 @@
       <c r="B134" t="s">
         <v>541</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="3" t="s">
         <v>542</v>
       </c>
       <c r="D134" t="s">
@@ -10652,7 +10744,7 @@
       <c r="B135" t="s">
         <v>547</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="3" t="s">
         <v>548</v>
       </c>
       <c r="D135" t="s">
@@ -10687,7 +10779,7 @@
       <c r="B136" t="s">
         <v>553</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="3" t="s">
         <v>554</v>
       </c>
       <c r="D136" t="s">
@@ -10722,7 +10814,7 @@
       <c r="B137" t="s">
         <v>558</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D137" t="s">
@@ -10757,7 +10849,7 @@
       <c r="B138" t="s">
         <v>562</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D138" t="s">
@@ -10792,8 +10884,8 @@
       <c r="B139" t="s">
         <v>567</v>
       </c>
-      <c r="C139">
-        <v>46211.418749999997</v>
+      <c r="C139" s="3" t="s">
+        <v>1933</v>
       </c>
       <c r="D139" t="s">
         <v>31</v>
@@ -10822,8 +10914,11 @@
       <c r="B140" t="s">
         <v>571</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="3" t="s">
         <v>367</v>
+      </c>
+      <c r="D140" t="s">
+        <v>31</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" t="s">
@@ -10846,8 +10941,8 @@
       <c r="B141" t="s">
         <v>575</v>
       </c>
-      <c r="C141">
-        <v>46184.438194444447</v>
+      <c r="C141" s="3" t="s">
+        <v>1929</v>
       </c>
       <c r="D141" t="s">
         <v>31</v>
@@ -10876,7 +10971,7 @@
       <c r="B142" t="s">
         <v>579</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="3" t="s">
         <v>387</v>
       </c>
       <c r="D142" t="s">
@@ -10911,7 +11006,7 @@
       <c r="B143" t="s">
         <v>582</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="3" t="s">
         <v>217</v>
       </c>
       <c r="D143" t="s">
@@ -10946,7 +11041,7 @@
       <c r="B144" t="s">
         <v>586</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="3" t="s">
         <v>109</v>
       </c>
       <c r="D144" t="s">
@@ -10981,7 +11076,7 @@
       <c r="B145" t="s">
         <v>591</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D145" t="s">
@@ -11016,7 +11111,7 @@
       <c r="B146" t="s">
         <v>594</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="3" t="s">
         <v>324</v>
       </c>
       <c r="D146" t="s">
@@ -11051,8 +11146,11 @@
       <c r="B147" t="s">
         <v>598</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="3" t="s">
         <v>735</v>
+      </c>
+      <c r="D147" t="s">
+        <v>58</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" t="s">
@@ -11075,7 +11173,7 @@
       <c r="B148" t="s">
         <v>602</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D148" t="s">
@@ -11110,7 +11208,7 @@
       <c r="B149" t="s">
         <v>606</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D149" t="s">
@@ -11145,7 +11243,7 @@
       <c r="B150" t="s">
         <v>610</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D150" t="s">
@@ -11180,7 +11278,7 @@
       <c r="B151" t="s">
         <v>614</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D151" t="s">
@@ -11215,7 +11313,7 @@
       <c r="B152" t="s">
         <v>617</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="3" t="s">
         <v>618</v>
       </c>
       <c r="D152" t="s">
@@ -11250,8 +11348,11 @@
       <c r="B153" t="s">
         <v>620</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="3" t="s">
         <v>848</v>
+      </c>
+      <c r="D153" t="s">
+        <v>58</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" t="s">
@@ -11274,8 +11375,11 @@
       <c r="B154" t="s">
         <v>623</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="3" t="s">
         <v>1272</v>
+      </c>
+      <c r="D154" t="s">
+        <v>58</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" t="s">
@@ -11298,7 +11402,7 @@
       <c r="B155" t="s">
         <v>626</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D155" t="s">
@@ -11333,7 +11437,7 @@
       <c r="B156" t="s">
         <v>628</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="3" t="s">
         <v>381</v>
       </c>
       <c r="D156" t="s">
@@ -11368,7 +11472,7 @@
       <c r="B157" t="s">
         <v>631</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D157" t="s">
@@ -11403,7 +11507,7 @@
       <c r="B158" t="s">
         <v>635</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D158" t="s">
@@ -11438,7 +11542,7 @@
       <c r="B159" t="s">
         <v>639</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="3" t="s">
         <v>640</v>
       </c>
       <c r="D159" t="s">
@@ -11473,7 +11577,7 @@
       <c r="B160" t="s">
         <v>643</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="3" t="s">
         <v>503</v>
       </c>
       <c r="D160" t="s">
@@ -11508,8 +11612,11 @@
       <c r="B161" t="s">
         <v>646</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="3" t="s">
         <v>188</v>
+      </c>
+      <c r="D161" t="s">
+        <v>31</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" t="s">
@@ -11532,7 +11639,7 @@
       <c r="B162" t="s">
         <v>650</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D162" t="s">
@@ -11564,8 +11671,11 @@
       <c r="B163" t="s">
         <v>653</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="3" t="s">
         <v>47</v>
+      </c>
+      <c r="D163" t="s">
+        <v>58</v>
       </c>
       <c r="F163" s="2"/>
       <c r="G163" t="s">
@@ -11588,7 +11698,7 @@
       <c r="B164" t="s">
         <v>657</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C164" s="3" t="s">
         <v>188</v>
       </c>
       <c r="D164" t="s">
@@ -11623,7 +11733,7 @@
       <c r="B165" t="s">
         <v>661</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="3" t="s">
         <v>507</v>
       </c>
       <c r="D165" t="s">
@@ -11658,7 +11768,7 @@
       <c r="B166" t="s">
         <v>665</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="3" t="s">
         <v>666</v>
       </c>
       <c r="D166" t="s">
@@ -11693,7 +11803,7 @@
       <c r="B167" t="s">
         <v>670</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D167" t="s">
@@ -11728,7 +11838,7 @@
       <c r="B168" t="s">
         <v>676</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="3" t="s">
         <v>618</v>
       </c>
       <c r="D168" t="s">
@@ -11763,7 +11873,7 @@
       <c r="B169" t="s">
         <v>681</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="3" t="s">
         <v>682</v>
       </c>
       <c r="D169" t="s">
@@ -11798,7 +11908,7 @@
       <c r="B170" t="s">
         <v>686</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="3" t="s">
         <v>687</v>
       </c>
       <c r="D170" t="s">
@@ -11833,8 +11943,11 @@
       <c r="B171" t="s">
         <v>693</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="3" t="s">
         <v>367</v>
+      </c>
+      <c r="D171" t="s">
+        <v>31</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" t="s">
@@ -11857,8 +11970,8 @@
       <c r="B172" t="s">
         <v>697</v>
       </c>
-      <c r="C172">
-        <v>46183.734027777777</v>
+      <c r="C172" s="3" t="s">
+        <v>1929</v>
       </c>
       <c r="D172" t="s">
         <v>31</v>
@@ -11887,7 +12000,7 @@
       <c r="B173" t="s">
         <v>700</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D173" t="s">
@@ -11922,7 +12035,7 @@
       <c r="B174" t="s">
         <v>705</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="3" t="s">
         <v>706</v>
       </c>
       <c r="D174" t="s">
@@ -11954,8 +12067,11 @@
       <c r="B175" t="s">
         <v>710</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="3" t="s">
         <v>350</v>
+      </c>
+      <c r="D175" t="s">
+        <v>58</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" t="s">
@@ -11978,7 +12094,7 @@
       <c r="B176" t="s">
         <v>714</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D176" t="s">
@@ -12013,7 +12129,7 @@
       <c r="B177" t="s">
         <v>719</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D177" t="s">
@@ -12048,8 +12164,11 @@
       <c r="B178" t="s">
         <v>723</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="D178" t="s">
+        <v>31</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" t="s">
@@ -12072,8 +12191,11 @@
       <c r="B179" t="s">
         <v>727</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="3" t="s">
         <v>409</v>
+      </c>
+      <c r="D179" t="s">
+        <v>58</v>
       </c>
       <c r="F179" s="2"/>
       <c r="G179" t="s">
@@ -12096,7 +12218,7 @@
       <c r="B180" t="s">
         <v>730</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D180" t="s">
@@ -12131,7 +12253,7 @@
       <c r="B181" t="s">
         <v>734</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="3" t="s">
         <v>735</v>
       </c>
       <c r="D181" t="s">
@@ -12166,7 +12288,7 @@
       <c r="B182" t="s">
         <v>740</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="3" t="s">
         <v>366</v>
       </c>
       <c r="D182" t="s">
@@ -12201,7 +12323,7 @@
       <c r="B183" t="s">
         <v>746</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D183" t="s">
@@ -12236,7 +12358,7 @@
       <c r="B184" t="s">
         <v>748</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D184" t="s">
@@ -12271,7 +12393,7 @@
       <c r="B185" t="s">
         <v>751</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D185" t="s">
@@ -12306,7 +12428,7 @@
       <c r="B186" t="s">
         <v>754</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C186" s="3" t="s">
         <v>755</v>
       </c>
       <c r="D186" t="s">
@@ -12341,7 +12463,7 @@
       <c r="B187" t="s">
         <v>758</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D187" t="s">
@@ -12376,7 +12498,7 @@
       <c r="B188" t="s">
         <v>760</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C188" s="3" t="s">
         <v>761</v>
       </c>
       <c r="D188" t="s">
@@ -12411,7 +12533,7 @@
       <c r="B189" t="s">
         <v>764</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="3" t="s">
         <v>765</v>
       </c>
       <c r="D189" t="s">
@@ -12446,7 +12568,7 @@
       <c r="B190" t="s">
         <v>767</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C190" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D190" t="s">
@@ -12481,7 +12603,7 @@
       <c r="B191" t="s">
         <v>769</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D191" t="s">
@@ -12516,7 +12638,7 @@
       <c r="B192" t="s">
         <v>771</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C192" s="3" t="s">
         <v>765</v>
       </c>
       <c r="D192" t="s">
@@ -12551,7 +12673,7 @@
       <c r="B193" t="s">
         <v>772</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C193" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D193" t="s">
@@ -12586,7 +12708,7 @@
       <c r="B194" t="s">
         <v>775</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="3" t="s">
         <v>761</v>
       </c>
       <c r="D194" t="s">
@@ -12621,7 +12743,7 @@
       <c r="B195" t="s">
         <v>778</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C195" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D195" t="s">
@@ -12656,7 +12778,7 @@
       <c r="B196" t="s">
         <v>783</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D196" t="s">
@@ -12691,7 +12813,7 @@
       <c r="B197" t="s">
         <v>787</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C197" s="3" t="s">
         <v>666</v>
       </c>
       <c r="D197" t="s">
@@ -12726,7 +12848,7 @@
       <c r="B198" t="s">
         <v>792</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C198" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D198" t="s">
@@ -12758,7 +12880,7 @@
       <c r="B199" t="s">
         <v>798</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="3" t="s">
         <v>761</v>
       </c>
       <c r="D199" t="s">
@@ -12793,7 +12915,7 @@
       <c r="B200" t="s">
         <v>802</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C200" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D200" t="s">
@@ -12828,7 +12950,7 @@
       <c r="B201" t="s">
         <v>805</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C201" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D201" t="s">
@@ -12863,7 +12985,7 @@
       <c r="B202" t="s">
         <v>808</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C202" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D202" t="s">
@@ -12898,7 +13020,7 @@
       <c r="B203" t="s">
         <v>811</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C203" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D203" t="s">
@@ -12933,7 +13055,7 @@
       <c r="B204" t="s">
         <v>814</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C204" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D204" t="s">
@@ -12968,7 +13090,7 @@
       <c r="B205" t="s">
         <v>817</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C205" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D205" t="s">
@@ -13003,7 +13125,7 @@
       <c r="B206" t="s">
         <v>820</v>
       </c>
-      <c r="C206" t="s">
+      <c r="C206" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D206" t="s">
@@ -13038,8 +13160,11 @@
       <c r="B207" t="s">
         <v>824</v>
       </c>
-      <c r="C207" t="s">
+      <c r="C207" s="3" t="s">
         <v>188</v>
+      </c>
+      <c r="D207" t="s">
+        <v>31</v>
       </c>
       <c r="F207" s="2"/>
       <c r="G207" t="s">
@@ -13062,8 +13187,11 @@
       <c r="B208" t="s">
         <v>828</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C208" s="3" t="s">
         <v>367</v>
+      </c>
+      <c r="D208" t="s">
+        <v>31</v>
       </c>
       <c r="F208" s="2"/>
       <c r="G208" t="s">
@@ -13086,7 +13214,7 @@
       <c r="B209" t="s">
         <v>831</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C209" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D209" t="s">
@@ -13121,7 +13249,7 @@
       <c r="B210" t="s">
         <v>835</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C210" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D210" t="s">
@@ -13156,7 +13284,7 @@
       <c r="B211" t="s">
         <v>839</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C211" s="3" t="s">
         <v>840</v>
       </c>
       <c r="D211" t="s">
@@ -13191,7 +13319,7 @@
       <c r="B212" t="s">
         <v>843</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C212" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D212" t="s">
@@ -13226,7 +13354,7 @@
       <c r="B213" t="s">
         <v>847</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C213" s="3" t="s">
         <v>848</v>
       </c>
       <c r="D213" t="s">
@@ -13261,7 +13389,7 @@
       <c r="B214" t="s">
         <v>851</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C214" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D214" t="s">
@@ -13296,8 +13424,11 @@
       <c r="B215" t="s">
         <v>855</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C215" s="3" t="s">
         <v>183</v>
+      </c>
+      <c r="D215" t="s">
+        <v>58</v>
       </c>
       <c r="F215" s="2"/>
       <c r="G215" t="s">
@@ -13320,7 +13451,7 @@
       <c r="B216" t="s">
         <v>858</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C216" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D216" t="s">
@@ -13355,7 +13486,7 @@
       <c r="B217" t="s">
         <v>862</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C217" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D217" t="s">
@@ -13390,7 +13521,7 @@
       <c r="B218" t="s">
         <v>864</v>
       </c>
-      <c r="C218" t="s">
+      <c r="C218" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D218" t="s">
@@ -13425,7 +13556,7 @@
       <c r="B219" t="s">
         <v>867</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C219" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D219" t="s">
@@ -13460,7 +13591,7 @@
       <c r="B220" t="s">
         <v>870</v>
       </c>
-      <c r="C220" t="s">
+      <c r="C220" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D220" t="s">
@@ -13495,7 +13626,7 @@
       <c r="B221" t="s">
         <v>873</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C221" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D221" t="s">
@@ -13530,7 +13661,7 @@
       <c r="B222" t="s">
         <v>876</v>
       </c>
-      <c r="C222" t="s">
+      <c r="C222" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D222" t="s">
@@ -13565,7 +13696,7 @@
       <c r="B223" t="s">
         <v>879</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C223" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D223" t="s">
@@ -13600,7 +13731,7 @@
       <c r="B224" t="s">
         <v>882</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C224" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D224" t="s">
@@ -13635,7 +13766,7 @@
       <c r="B225" t="s">
         <v>885</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C225" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D225" t="s">
@@ -13670,7 +13801,7 @@
       <c r="B226" t="s">
         <v>887</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C226" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D226" t="s">
@@ -13705,7 +13836,7 @@
       <c r="B227" t="s">
         <v>890</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C227" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D227" t="s">
@@ -13740,7 +13871,7 @@
       <c r="B228" t="s">
         <v>892</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C228" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D228" t="s">
@@ -13775,7 +13906,7 @@
       <c r="B229" t="s">
         <v>895</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D229" t="s">
@@ -13810,8 +13941,8 @@
       <c r="B230" t="s">
         <v>898</v>
       </c>
-      <c r="C230">
-        <v>45968.125</v>
+      <c r="C230" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D230" t="s">
         <v>31</v>
@@ -13840,7 +13971,7 @@
       <c r="B231" t="s">
         <v>902</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C231" s="3" t="s">
         <v>903</v>
       </c>
       <c r="D231" t="s">
@@ -13875,8 +14006,11 @@
       <c r="B232" t="s">
         <v>907</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C232" s="3" t="s">
         <v>367</v>
+      </c>
+      <c r="D232" t="s">
+        <v>31</v>
       </c>
       <c r="F232" s="2"/>
       <c r="G232" t="s">
@@ -13899,8 +14033,11 @@
       <c r="B233" t="s">
         <v>911</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C233" s="3" t="s">
         <v>188</v>
+      </c>
+      <c r="D233" t="s">
+        <v>31</v>
       </c>
       <c r="F233" s="2"/>
       <c r="G233" t="s">
@@ -13923,7 +14060,7 @@
       <c r="B234" t="s">
         <v>914</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C234" s="3" t="s">
         <v>381</v>
       </c>
       <c r="D234" t="s">
@@ -13958,7 +14095,7 @@
       <c r="B235" t="s">
         <v>917</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C235" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D235" t="s">
@@ -13993,8 +14130,11 @@
       <c r="B236" t="s">
         <v>921</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C236" s="3" t="s">
         <v>1933</v>
+      </c>
+      <c r="D236" t="s">
+        <v>31</v>
       </c>
       <c r="F236" s="2"/>
       <c r="G236" t="s">
@@ -14017,7 +14157,7 @@
       <c r="B237" t="s">
         <v>924</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C237" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D237" t="s">
@@ -14052,7 +14192,7 @@
       <c r="B238" t="s">
         <v>926</v>
       </c>
-      <c r="C238" t="s">
+      <c r="C238" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D238" t="s">
@@ -14087,7 +14227,7 @@
       <c r="B239" t="s">
         <v>928</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C239" s="3" t="s">
         <v>507</v>
       </c>
       <c r="D239" t="s">
@@ -14122,7 +14262,7 @@
       <c r="B240" t="s">
         <v>932</v>
       </c>
-      <c r="C240" t="s">
+      <c r="C240" s="3" t="s">
         <v>933</v>
       </c>
       <c r="D240" t="s">
@@ -14157,7 +14297,7 @@
       <c r="B241" t="s">
         <v>937</v>
       </c>
-      <c r="C241" t="s">
+      <c r="C241" s="3" t="s">
         <v>761</v>
       </c>
       <c r="D241" t="s">
@@ -14192,8 +14332,11 @@
       <c r="B242" t="s">
         <v>940</v>
       </c>
-      <c r="C242" t="s">
+      <c r="C242" s="3" t="s">
         <v>387</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1939</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" t="s">
@@ -14216,8 +14359,11 @@
       <c r="B243" t="s">
         <v>943</v>
       </c>
-      <c r="C243" t="s">
+      <c r="C243" s="3" t="s">
         <v>57</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1939</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" t="s">
@@ -14240,7 +14386,7 @@
       <c r="B244" t="s">
         <v>946</v>
       </c>
-      <c r="C244" t="s">
+      <c r="C244" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D244" t="s">
@@ -14275,7 +14421,7 @@
       <c r="B245" t="s">
         <v>949</v>
       </c>
-      <c r="C245" t="s">
+      <c r="C245" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D245" t="s">
@@ -14310,7 +14456,7 @@
       <c r="B246" t="s">
         <v>952</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C246" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D246" t="s">
@@ -14345,7 +14491,7 @@
       <c r="B247" t="s">
         <v>955</v>
       </c>
-      <c r="C247" t="s">
+      <c r="C247" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D247" t="s">
@@ -14380,7 +14526,7 @@
       <c r="B248" t="s">
         <v>959</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C248" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D248" t="s">
@@ -14415,7 +14561,7 @@
       <c r="B249" t="s">
         <v>962</v>
       </c>
-      <c r="C249" t="s">
+      <c r="C249" s="3" t="s">
         <v>963</v>
       </c>
       <c r="D249" t="s">
@@ -14450,7 +14596,7 @@
       <c r="B250" t="s">
         <v>966</v>
       </c>
-      <c r="C250" t="s">
+      <c r="C250" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D250" t="s">
@@ -14485,7 +14631,7 @@
       <c r="B251" t="s">
         <v>969</v>
       </c>
-      <c r="C251" t="s">
+      <c r="C251" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D251" t="s">
@@ -14520,7 +14666,7 @@
       <c r="B252" t="s">
         <v>973</v>
       </c>
-      <c r="C252" t="s">
+      <c r="C252" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D252" t="s">
@@ -14555,7 +14701,7 @@
       <c r="B253" t="s">
         <v>977</v>
       </c>
-      <c r="C253" t="s">
+      <c r="C253" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D253" t="s">
@@ -14590,8 +14736,11 @@
       <c r="B254" t="s">
         <v>980</v>
       </c>
-      <c r="C254" t="s">
+      <c r="C254" s="3" t="s">
         <v>1933</v>
+      </c>
+      <c r="D254" t="s">
+        <v>31</v>
       </c>
       <c r="F254" s="2"/>
       <c r="G254" t="s">
@@ -14614,8 +14763,11 @@
       <c r="B255" t="s">
         <v>983</v>
       </c>
-      <c r="C255" t="s">
+      <c r="C255" s="3" t="s">
         <v>30</v>
+      </c>
+      <c r="D255" t="s">
+        <v>58</v>
       </c>
       <c r="F255" s="2"/>
       <c r="G255" t="s">
@@ -14638,7 +14790,7 @@
       <c r="B256" t="s">
         <v>985</v>
       </c>
-      <c r="C256" t="s">
+      <c r="C256" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D256" t="s">
@@ -14673,7 +14825,7 @@
       <c r="B257" t="s">
         <v>988</v>
       </c>
-      <c r="C257" t="s">
+      <c r="C257" s="3" t="s">
         <v>640</v>
       </c>
       <c r="D257" t="s">
@@ -14708,7 +14860,7 @@
       <c r="B258" t="s">
         <v>992</v>
       </c>
-      <c r="C258" t="s">
+      <c r="C258" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D258" t="s">
@@ -14743,7 +14895,7 @@
       <c r="B259" t="s">
         <v>996</v>
       </c>
-      <c r="C259" t="s">
+      <c r="C259" s="3" t="s">
         <v>507</v>
       </c>
       <c r="D259" t="s">
@@ -14772,7 +14924,7 @@
       <c r="B260" t="s">
         <v>1000</v>
       </c>
-      <c r="C260" t="s">
+      <c r="C260" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D260" t="s">
@@ -14807,7 +14959,7 @@
       <c r="B261" t="s">
         <v>1004</v>
       </c>
-      <c r="C261" t="s">
+      <c r="C261" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D261" t="s">
@@ -14842,7 +14994,7 @@
       <c r="B262" t="s">
         <v>1007</v>
       </c>
-      <c r="C262" t="s">
+      <c r="C262" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D262" t="s">
@@ -14877,8 +15029,8 @@
       <c r="B263" t="s">
         <v>1012</v>
       </c>
-      <c r="C263">
-        <v>46266.125</v>
+      <c r="C263" s="3" t="s">
+        <v>1937</v>
       </c>
       <c r="D263" t="s">
         <v>31</v>
@@ -14907,7 +15059,7 @@
       <c r="B264" t="s">
         <v>1015</v>
       </c>
-      <c r="C264" t="s">
+      <c r="C264" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D264" t="s">
@@ -14942,7 +15094,7 @@
       <c r="B265" t="s">
         <v>1018</v>
       </c>
-      <c r="C265" t="s">
+      <c r="C265" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D265" t="s">
@@ -14977,7 +15129,7 @@
       <c r="B266" t="s">
         <v>1021</v>
       </c>
-      <c r="C266" t="s">
+      <c r="C266" s="3" t="s">
         <v>755</v>
       </c>
       <c r="D266" t="s">
@@ -15012,7 +15164,7 @@
       <c r="B267" t="s">
         <v>1024</v>
       </c>
-      <c r="C267" t="s">
+      <c r="C267" s="3" t="s">
         <v>666</v>
       </c>
       <c r="D267" t="s">
@@ -15047,8 +15199,11 @@
       <c r="B268" t="s">
         <v>1027</v>
       </c>
-      <c r="C268" t="s">
+      <c r="C268" s="3" t="s">
         <v>1272</v>
+      </c>
+      <c r="D268" t="s">
+        <v>58</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" t="s">
@@ -15071,7 +15226,7 @@
       <c r="B269" t="s">
         <v>1030</v>
       </c>
-      <c r="C269" t="s">
+      <c r="C269" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D269" t="s">
@@ -15106,7 +15261,7 @@
       <c r="B270" t="s">
         <v>1032</v>
       </c>
-      <c r="C270" t="s">
+      <c r="C270" s="3" t="s">
         <v>1033</v>
       </c>
       <c r="D270" t="s">
@@ -15141,7 +15296,7 @@
       <c r="B271" t="s">
         <v>1035</v>
       </c>
-      <c r="C271" t="s">
+      <c r="C271" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D271" t="s">
@@ -15176,7 +15331,7 @@
       <c r="B272" t="s">
         <v>1037</v>
       </c>
-      <c r="C272" t="s">
+      <c r="C272" s="3" t="s">
         <v>1038</v>
       </c>
       <c r="D272" t="s">
@@ -15211,8 +15366,11 @@
       <c r="B273" t="s">
         <v>1040</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C273" s="3" t="s">
         <v>350</v>
+      </c>
+      <c r="D273" t="s">
+        <v>58</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" t="s">
@@ -15235,8 +15393,11 @@
       <c r="B274" t="s">
         <v>1043</v>
       </c>
-      <c r="C274" t="s">
+      <c r="C274" s="3" t="s">
         <v>350</v>
+      </c>
+      <c r="D274" t="s">
+        <v>58</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" t="s">
@@ -15259,7 +15420,7 @@
       <c r="B275" t="s">
         <v>1046</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C275" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D275" t="s">
@@ -15294,7 +15455,7 @@
       <c r="B276" t="s">
         <v>1048</v>
       </c>
-      <c r="C276" t="s">
+      <c r="C276" s="3" t="s">
         <v>666</v>
       </c>
       <c r="D276" t="s">
@@ -15329,7 +15490,7 @@
       <c r="B277" t="s">
         <v>1051</v>
       </c>
-      <c r="C277" t="s">
+      <c r="C277" s="3" t="s">
         <v>765</v>
       </c>
       <c r="D277" t="s">
@@ -15364,7 +15525,7 @@
       <c r="B278" t="s">
         <v>1054</v>
       </c>
-      <c r="C278" t="s">
+      <c r="C278" s="3" t="s">
         <v>666</v>
       </c>
       <c r="D278" t="s">
@@ -15399,7 +15560,7 @@
       <c r="B279" t="s">
         <v>1056</v>
       </c>
-      <c r="C279" t="s">
+      <c r="C279" s="3" t="s">
         <v>1057</v>
       </c>
       <c r="D279" t="s">
@@ -15434,7 +15595,7 @@
       <c r="B280" t="s">
         <v>1060</v>
       </c>
-      <c r="C280" t="s">
+      <c r="C280" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D280" t="s">
@@ -15469,8 +15630,11 @@
       <c r="B281" t="s">
         <v>1063</v>
       </c>
-      <c r="C281" t="s">
+      <c r="C281" s="3" t="s">
         <v>1929</v>
+      </c>
+      <c r="D281" t="s">
+        <v>31</v>
       </c>
       <c r="F281" s="2"/>
       <c r="G281" t="s">
@@ -15493,7 +15657,7 @@
       <c r="B282" t="s">
         <v>1065</v>
       </c>
-      <c r="C282" t="s">
+      <c r="C282" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D282" t="s">
@@ -15528,7 +15692,7 @@
       <c r="B283" t="s">
         <v>1068</v>
       </c>
-      <c r="C283" t="s">
+      <c r="C283" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D283" t="s">
@@ -15563,7 +15727,7 @@
       <c r="B284" t="s">
         <v>1071</v>
       </c>
-      <c r="C284" t="s">
+      <c r="C284" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D284" t="s">
@@ -15598,7 +15762,7 @@
       <c r="B285" t="s">
         <v>1073</v>
       </c>
-      <c r="C285" t="s">
+      <c r="C285" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D285" t="s">
@@ -15633,7 +15797,7 @@
       <c r="B286" t="s">
         <v>1076</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C286" s="3" t="s">
         <v>1077</v>
       </c>
       <c r="D286" t="s">
@@ -15668,7 +15832,7 @@
       <c r="B287" t="s">
         <v>1080</v>
       </c>
-      <c r="C287" t="s">
+      <c r="C287" s="3" t="s">
         <v>666</v>
       </c>
       <c r="D287" t="s">
@@ -15703,7 +15867,7 @@
       <c r="B288" t="s">
         <v>1084</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C288" s="3" t="s">
         <v>313</v>
       </c>
       <c r="D288" t="s">
@@ -15733,8 +15897,11 @@
       <c r="B289" t="s">
         <v>1087</v>
       </c>
-      <c r="C289" t="s">
+      <c r="C289" s="3" t="s">
         <v>1929</v>
+      </c>
+      <c r="D289" t="s">
+        <v>31</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" t="s">
@@ -15757,7 +15924,7 @@
       <c r="B290" t="s">
         <v>1091</v>
       </c>
-      <c r="C290" t="s">
+      <c r="C290" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D290" t="s">
@@ -15792,7 +15959,7 @@
       <c r="B291" t="s">
         <v>1093</v>
       </c>
-      <c r="C291" t="s">
+      <c r="C291" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D291" t="s">
@@ -15827,7 +15994,7 @@
       <c r="B292" t="s">
         <v>1095</v>
       </c>
-      <c r="C292" t="s">
+      <c r="C292" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D292" t="s">
@@ -15862,7 +16029,7 @@
       <c r="B293" t="s">
         <v>1098</v>
       </c>
-      <c r="C293" t="s">
+      <c r="C293" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D293" t="s">
@@ -15897,7 +16064,7 @@
       <c r="B294" t="s">
         <v>1102</v>
       </c>
-      <c r="C294" t="s">
+      <c r="C294" s="3" t="s">
         <v>682</v>
       </c>
       <c r="D294" t="s">
@@ -15932,7 +16099,7 @@
       <c r="B295" t="s">
         <v>1105</v>
       </c>
-      <c r="C295" t="s">
+      <c r="C295" s="3" t="s">
         <v>488</v>
       </c>
       <c r="D295" t="s">
@@ -15967,7 +16134,7 @@
       <c r="B296" t="s">
         <v>1110</v>
       </c>
-      <c r="C296" t="s">
+      <c r="C296" s="3" t="s">
         <v>484</v>
       </c>
       <c r="D296" t="s">
@@ -16002,7 +16169,7 @@
       <c r="B297" t="s">
         <v>1114</v>
       </c>
-      <c r="C297" t="s">
+      <c r="C297" s="3" t="s">
         <v>1115</v>
       </c>
       <c r="D297" t="s">
@@ -16037,7 +16204,7 @@
       <c r="B298" t="s">
         <v>1119</v>
       </c>
-      <c r="C298" t="s">
+      <c r="C298" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D298" t="s">
@@ -16072,7 +16239,7 @@
       <c r="B299" t="s">
         <v>1123</v>
       </c>
-      <c r="C299" t="s">
+      <c r="C299" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D299" t="s">
@@ -16107,8 +16274,8 @@
       <c r="B300" t="s">
         <v>1127</v>
       </c>
-      <c r="C300">
-        <v>46210.443749999999</v>
+      <c r="C300" s="3" t="s">
+        <v>1933</v>
       </c>
       <c r="D300" t="s">
         <v>31</v>
@@ -16137,7 +16304,7 @@
       <c r="B301" t="s">
         <v>1129</v>
       </c>
-      <c r="C301" t="s">
+      <c r="C301" s="3" t="s">
         <v>381</v>
       </c>
       <c r="D301" t="s">
@@ -16172,7 +16339,7 @@
       <c r="B302" t="s">
         <v>1132</v>
       </c>
-      <c r="C302" t="s">
+      <c r="C302" s="3" t="s">
         <v>1133</v>
       </c>
       <c r="D302" t="s">
@@ -16207,7 +16374,7 @@
       <c r="B303" t="s">
         <v>1137</v>
       </c>
-      <c r="C303" t="s">
+      <c r="C303" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D303" t="s">
@@ -16242,8 +16409,11 @@
       <c r="B304" t="s">
         <v>1140</v>
       </c>
-      <c r="C304" t="s">
+      <c r="C304" s="3" t="s">
         <v>188</v>
+      </c>
+      <c r="D304" t="s">
+        <v>31</v>
       </c>
       <c r="F304" s="2"/>
       <c r="G304" t="s">
@@ -16266,7 +16436,7 @@
       <c r="B305" t="s">
         <v>1143</v>
       </c>
-      <c r="C305" t="s">
+      <c r="C305" s="3" t="s">
         <v>765</v>
       </c>
       <c r="D305" t="s">
@@ -16301,7 +16471,7 @@
       <c r="B306" t="s">
         <v>1148</v>
       </c>
-      <c r="C306" t="s">
+      <c r="C306" s="3" t="s">
         <v>618</v>
       </c>
       <c r="D306" t="s">
@@ -16336,7 +16506,7 @@
       <c r="B307" t="s">
         <v>1152</v>
       </c>
-      <c r="C307" t="s">
+      <c r="C307" s="3" t="s">
         <v>1153</v>
       </c>
       <c r="D307" t="s">
@@ -16371,7 +16541,7 @@
       <c r="B308" t="s">
         <v>1157</v>
       </c>
-      <c r="C308" t="s">
+      <c r="C308" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D308" t="s">
@@ -16406,7 +16576,7 @@
       <c r="B309" t="s">
         <v>1162</v>
       </c>
-      <c r="C309" t="s">
+      <c r="C309" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D309" t="s">
@@ -16441,7 +16611,7 @@
       <c r="B310" t="s">
         <v>1166</v>
       </c>
-      <c r="C310" t="s">
+      <c r="C310" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D310" t="s">
@@ -16476,7 +16646,7 @@
       <c r="B311" t="s">
         <v>1168</v>
       </c>
-      <c r="C311" t="s">
+      <c r="C311" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D311" t="s">
@@ -16511,7 +16681,7 @@
       <c r="B312" t="s">
         <v>1170</v>
       </c>
-      <c r="C312" t="s">
+      <c r="C312" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D312" t="s">
@@ -16546,7 +16716,7 @@
       <c r="B313" t="s">
         <v>1173</v>
       </c>
-      <c r="C313" t="s">
+      <c r="C313" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D313" t="s">
@@ -16581,7 +16751,7 @@
       <c r="B314" t="s">
         <v>1177</v>
       </c>
-      <c r="C314" t="s">
+      <c r="C314" s="3" t="s">
         <v>366</v>
       </c>
       <c r="D314" t="s">
@@ -16613,7 +16783,7 @@
       <c r="B315" t="s">
         <v>1183</v>
       </c>
-      <c r="C315" t="s">
+      <c r="C315" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D315" t="s">
@@ -16648,7 +16818,7 @@
       <c r="B316" t="s">
         <v>1187</v>
       </c>
-      <c r="C316" t="s">
+      <c r="C316" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D316" t="s">
@@ -16683,7 +16853,7 @@
       <c r="B317" t="s">
         <v>1190</v>
       </c>
-      <c r="C317" t="s">
+      <c r="C317" s="3" t="s">
         <v>903</v>
       </c>
       <c r="D317" t="s">
@@ -16718,7 +16888,7 @@
       <c r="B318" t="s">
         <v>1193</v>
       </c>
-      <c r="C318" t="s">
+      <c r="C318" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D318" t="s">
@@ -16753,7 +16923,7 @@
       <c r="B319" t="s">
         <v>1196</v>
       </c>
-      <c r="C319" t="s">
+      <c r="C319" s="3" t="s">
         <v>387</v>
       </c>
       <c r="D319" t="s">
@@ -16788,7 +16958,7 @@
       <c r="B320" t="s">
         <v>1200</v>
       </c>
-      <c r="C320" t="s">
+      <c r="C320" s="3" t="s">
         <v>1201</v>
       </c>
       <c r="D320" t="s">
@@ -16823,7 +16993,7 @@
       <c r="B321" t="s">
         <v>1205</v>
       </c>
-      <c r="C321" t="s">
+      <c r="C321" s="3" t="s">
         <v>1133</v>
       </c>
       <c r="D321" t="s">
@@ -16858,7 +17028,7 @@
       <c r="B322" t="s">
         <v>1208</v>
       </c>
-      <c r="C322" t="s">
+      <c r="C322" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D322" t="s">
@@ -16893,7 +17063,7 @@
       <c r="B323" t="s">
         <v>1211</v>
       </c>
-      <c r="C323" t="s">
+      <c r="C323" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D323" t="s">
@@ -16928,7 +17098,7 @@
       <c r="B324" t="s">
         <v>1214</v>
       </c>
-      <c r="C324" t="s">
+      <c r="C324" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D324" t="s">
@@ -16963,7 +17133,7 @@
       <c r="B325" t="s">
         <v>1217</v>
       </c>
-      <c r="C325" t="s">
+      <c r="C325" s="3" t="s">
         <v>903</v>
       </c>
       <c r="D325" t="s">
@@ -16998,7 +17168,7 @@
       <c r="B326" t="s">
         <v>1219</v>
       </c>
-      <c r="C326" t="s">
+      <c r="C326" s="3" t="s">
         <v>507</v>
       </c>
       <c r="D326" t="s">
@@ -17033,7 +17203,7 @@
       <c r="B327" t="s">
         <v>1222</v>
       </c>
-      <c r="C327" t="s">
+      <c r="C327" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D327" t="s">
@@ -17068,7 +17238,7 @@
       <c r="B328" t="s">
         <v>1224</v>
       </c>
-      <c r="C328" t="s">
+      <c r="C328" s="3" t="s">
         <v>409</v>
       </c>
       <c r="D328" t="s">
@@ -17103,7 +17273,7 @@
       <c r="B329" t="s">
         <v>1227</v>
       </c>
-      <c r="C329" t="s">
+      <c r="C329" s="3" t="s">
         <v>903</v>
       </c>
       <c r="D329" t="s">
@@ -17138,7 +17308,7 @@
       <c r="B330" t="s">
         <v>1230</v>
       </c>
-      <c r="C330" t="s">
+      <c r="C330" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D330" t="s">
@@ -17173,7 +17343,7 @@
       <c r="B331" t="s">
         <v>1233</v>
       </c>
-      <c r="C331" t="s">
+      <c r="C331" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D331" t="s">
@@ -17208,7 +17378,7 @@
       <c r="B332" t="s">
         <v>1237</v>
       </c>
-      <c r="C332" t="s">
+      <c r="C332" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D332" t="s">
@@ -17243,7 +17413,7 @@
       <c r="B333" t="s">
         <v>1239</v>
       </c>
-      <c r="C333" t="s">
+      <c r="C333" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D333" t="s">
@@ -17278,7 +17448,7 @@
       <c r="B334" t="s">
         <v>1242</v>
       </c>
-      <c r="C334" t="s">
+      <c r="C334" s="3" t="s">
         <v>1243</v>
       </c>
       <c r="D334" t="s">
@@ -17313,7 +17483,7 @@
       <c r="B335" t="s">
         <v>1246</v>
       </c>
-      <c r="C335" t="s">
+      <c r="C335" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D335" t="s">
@@ -17348,7 +17518,7 @@
       <c r="B336" t="s">
         <v>1249</v>
       </c>
-      <c r="C336" t="s">
+      <c r="C336" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D336" t="s">
@@ -17383,7 +17553,7 @@
       <c r="B337" t="s">
         <v>1253</v>
       </c>
-      <c r="C337" t="s">
+      <c r="C337" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D337" t="s">
@@ -17418,7 +17588,7 @@
       <c r="B338" t="s">
         <v>1255</v>
       </c>
-      <c r="C338" t="s">
+      <c r="C338" s="3" t="s">
         <v>840</v>
       </c>
       <c r="D338" t="s">
@@ -17453,7 +17623,7 @@
       <c r="B339" t="s">
         <v>1258</v>
       </c>
-      <c r="C339" t="s">
+      <c r="C339" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D339" t="s">
@@ -17488,7 +17658,7 @@
       <c r="B340" t="s">
         <v>1261</v>
       </c>
-      <c r="C340" t="s">
+      <c r="C340" s="3" t="s">
         <v>171</v>
       </c>
       <c r="D340" t="s">
@@ -17523,8 +17693,11 @@
       <c r="B341" t="s">
         <v>1264</v>
       </c>
-      <c r="C341" t="s">
+      <c r="C341" s="3" t="s">
         <v>388</v>
+      </c>
+      <c r="D341" t="s">
+        <v>31</v>
       </c>
       <c r="F341" s="2"/>
       <c r="G341" t="s">
@@ -17547,7 +17720,7 @@
       <c r="B342" t="s">
         <v>1268</v>
       </c>
-      <c r="C342" t="s">
+      <c r="C342" s="3" t="s">
         <v>507</v>
       </c>
       <c r="D342" t="s">
@@ -17582,7 +17755,7 @@
       <c r="B343" t="s">
         <v>1271</v>
       </c>
-      <c r="C343" t="s">
+      <c r="C343" s="3" t="s">
         <v>1272</v>
       </c>
       <c r="D343" t="s">
@@ -17617,7 +17790,7 @@
       <c r="B344" t="s">
         <v>1277</v>
       </c>
-      <c r="C344" t="s">
+      <c r="C344" s="3" t="s">
         <v>1272</v>
       </c>
       <c r="D344" t="s">
@@ -17652,7 +17825,7 @@
       <c r="B345" t="s">
         <v>1281</v>
       </c>
-      <c r="C345" t="s">
+      <c r="C345" s="3" t="s">
         <v>109</v>
       </c>
       <c r="D345" t="s">
@@ -17687,7 +17860,7 @@
       <c r="B346" t="s">
         <v>1283</v>
       </c>
-      <c r="C346" t="s">
+      <c r="C346" s="3" t="s">
         <v>761</v>
       </c>
       <c r="D346" t="s">
@@ -17722,7 +17895,7 @@
       <c r="B347" t="s">
         <v>1287</v>
       </c>
-      <c r="C347" t="s">
+      <c r="C347" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D347" t="s">
@@ -17757,8 +17930,11 @@
       <c r="B348" t="s">
         <v>1291</v>
       </c>
-      <c r="C348" t="s">
+      <c r="C348" s="3" t="s">
         <v>14</v>
+      </c>
+      <c r="D348" t="s">
+        <v>58</v>
       </c>
       <c r="F348" s="2"/>
       <c r="G348" t="s">
@@ -17781,7 +17957,7 @@
       <c r="B349" t="s">
         <v>1294</v>
       </c>
-      <c r="C349" t="s">
+      <c r="C349" s="3" t="s">
         <v>484</v>
       </c>
       <c r="D349" t="s">
@@ -17816,7 +17992,7 @@
       <c r="B350" t="s">
         <v>1298</v>
       </c>
-      <c r="C350" t="s">
+      <c r="C350" s="3" t="s">
         <v>324</v>
       </c>
       <c r="D350" t="s">
@@ -17851,7 +18027,7 @@
       <c r="B351" t="s">
         <v>1302</v>
       </c>
-      <c r="C351" t="s">
+      <c r="C351" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D351" t="s">
@@ -17886,7 +18062,7 @@
       <c r="B352" t="s">
         <v>1305</v>
       </c>
-      <c r="C352" t="s">
+      <c r="C352" s="3" t="s">
         <v>387</v>
       </c>
       <c r="D352" t="s">
@@ -17921,7 +18097,7 @@
       <c r="B353" t="s">
         <v>1309</v>
       </c>
-      <c r="C353" t="s">
+      <c r="C353" s="3" t="s">
         <v>640</v>
       </c>
       <c r="D353" t="s">
@@ -17956,7 +18132,7 @@
       <c r="B354" t="s">
         <v>1313</v>
       </c>
-      <c r="C354" t="s">
+      <c r="C354" s="3" t="s">
         <v>507</v>
       </c>
       <c r="D354" t="s">
@@ -17991,7 +18167,7 @@
       <c r="B355" t="s">
         <v>1317</v>
       </c>
-      <c r="C355" t="s">
+      <c r="C355" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D355" t="s">
@@ -18026,7 +18202,7 @@
       <c r="B356" t="s">
         <v>1321</v>
       </c>
-      <c r="C356" t="s">
+      <c r="C356" s="3" t="s">
         <v>1322</v>
       </c>
       <c r="D356" t="s">
@@ -18058,7 +18234,7 @@
       <c r="B357" t="s">
         <v>1326</v>
       </c>
-      <c r="C357" t="s">
+      <c r="C357" s="3" t="s">
         <v>503</v>
       </c>
       <c r="D357" t="s">
@@ -18093,7 +18269,7 @@
       <c r="B358" t="s">
         <v>1329</v>
       </c>
-      <c r="C358" t="s">
+      <c r="C358" s="3" t="s">
         <v>507</v>
       </c>
       <c r="D358" t="s">
@@ -18128,7 +18304,7 @@
       <c r="B359" t="s">
         <v>1334</v>
       </c>
-      <c r="C359" t="s">
+      <c r="C359" s="3" t="s">
         <v>735</v>
       </c>
       <c r="D359" t="s">
@@ -18163,7 +18339,7 @@
       <c r="B360" t="s">
         <v>1337</v>
       </c>
-      <c r="C360" t="s">
+      <c r="C360" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D360" t="s">
@@ -18198,7 +18374,7 @@
       <c r="B361" t="s">
         <v>1927</v>
       </c>
-      <c r="C361" t="s">
+      <c r="C361" s="3" t="s">
         <v>963</v>
       </c>
       <c r="D361" t="s">
@@ -18233,7 +18409,7 @@
       <c r="B362" t="s">
         <v>1344</v>
       </c>
-      <c r="C362" t="s">
+      <c r="C362" s="3" t="s">
         <v>963</v>
       </c>
       <c r="D362" t="s">
@@ -18268,7 +18444,7 @@
       <c r="B363" t="s">
         <v>1348</v>
       </c>
-      <c r="C363" t="s">
+      <c r="C363" s="3" t="s">
         <v>381</v>
       </c>
       <c r="D363" t="s">
@@ -18303,7 +18479,7 @@
       <c r="B364" t="s">
         <v>1352</v>
       </c>
-      <c r="C364" t="s">
+      <c r="C364" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D364" t="s">
@@ -18338,7 +18514,7 @@
       <c r="B365" t="s">
         <v>1356</v>
       </c>
-      <c r="C365" t="s">
+      <c r="C365" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D365" t="s">
@@ -18373,7 +18549,7 @@
       <c r="B366" t="s">
         <v>1359</v>
       </c>
-      <c r="C366" t="s">
+      <c r="C366" s="3" t="s">
         <v>735</v>
       </c>
       <c r="D366" t="s">
@@ -18408,7 +18584,7 @@
       <c r="B367" t="s">
         <v>1365</v>
       </c>
-      <c r="C367" t="s">
+      <c r="C367" s="3" t="s">
         <v>1366</v>
       </c>
       <c r="D367" t="s">

--- a/Mapa - Zelar.xlsx
+++ b/Mapa - Zelar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aguinir.junior\Desktop\Gestão\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C457FC2-50C9-4BED-A78A-241B1B51BCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09522C84-2D4D-42CC-84DE-05C55F760961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11485,7 +11485,7 @@
         <v>555</v>
       </c>
       <c r="L138" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/Mapa - Zelar.xlsx
+++ b/Mapa - Zelar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aguinir.junior\Desktop\Gestão\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB1A6B0-FD65-4F30-83A1-EBDC065173A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7C9D16-E73D-4149-80EC-4FBE1231D179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapa" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Contatos!$A$1:$J$311</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapa!$A$1:$L$367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapa!$A$1:$L$365</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4584" uniqueCount="1957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4600" uniqueCount="1984">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -5876,24 +5876,6 @@
     <t>VERIFICAR</t>
   </si>
   <si>
-    <t>OP. UNIDAS TRANSPORTE CANA - UVT</t>
-  </si>
-  <si>
-    <t>OPERAÇÃO FULL</t>
-  </si>
-  <si>
-    <t>VICENTINA</t>
-  </si>
-  <si>
-    <t>GH8Q+8G Vicentina, Mato Grosso do Sul</t>
-  </si>
-  <si>
-    <t>OPERAÇÃO UEL</t>
-  </si>
-  <si>
-    <t>4XPP+CR Guarujá - Rio Brilhante, MS</t>
-  </si>
-  <si>
     <t>JANEIRO/26</t>
   </si>
   <si>
@@ -5913,6 +5895,105 @@
   </si>
   <si>
     <t>TERCEIRIZAÇÃO</t>
+  </si>
+  <si>
+    <t>57.864.574/0001-25</t>
+  </si>
+  <si>
+    <t>87.700.746/0015-91</t>
+  </si>
+  <si>
+    <t>41.867.410/0001-11</t>
+  </si>
+  <si>
+    <t>44.330.975/0031-79</t>
+  </si>
+  <si>
+    <t>03.833.915/0001-76</t>
+  </si>
+  <si>
+    <t>10.267.561/0001-05</t>
+  </si>
+  <si>
+    <t>09.323.098/0001-92</t>
+  </si>
+  <si>
+    <t>17.490.857/0001-30</t>
+  </si>
+  <si>
+    <t>75.444.430/0001-00</t>
+  </si>
+  <si>
+    <t>37.666.752/0001-04</t>
+  </si>
+  <si>
+    <t>11.192.347/0001-08</t>
+  </si>
+  <si>
+    <t>15.404.932/0002-58</t>
+  </si>
+  <si>
+    <t>08.800.028/0001-15</t>
+  </si>
+  <si>
+    <t>42.135.913/0002-46</t>
+  </si>
+  <si>
+    <t>00.609.820/0001-85</t>
+  </si>
+  <si>
+    <t>29.094.173/0001-06</t>
+  </si>
+  <si>
+    <t>40.408.094/0001-57</t>
+  </si>
+  <si>
+    <t>47.940.742/0008-37</t>
+  </si>
+  <si>
+    <t>03.310.685/0002-41</t>
+  </si>
+  <si>
+    <t>08.089.099/0001-51</t>
+  </si>
+  <si>
+    <t>21.752.910/0003-62</t>
+  </si>
+  <si>
+    <t>44.635.194/0001-77</t>
+  </si>
+  <si>
+    <t>12.898.982/0005-93</t>
+  </si>
+  <si>
+    <t>46.421.786/0001-11</t>
+  </si>
+  <si>
+    <t>75.703.256/0001-64</t>
+  </si>
+  <si>
+    <t>17.469.701/0001-77</t>
+  </si>
+  <si>
+    <t>692013340117</t>
+  </si>
+  <si>
+    <t>13.561.212-8</t>
+  </si>
+  <si>
+    <t>1250048009</t>
+  </si>
+  <si>
+    <t>33.453.598/0087-01</t>
+  </si>
+  <si>
+    <t>33.453.598/0045-44</t>
+  </si>
+  <si>
+    <t>04.011.297/0001-41</t>
+  </si>
+  <si>
+    <t>08.517.600/0001-33</t>
   </si>
 </sst>
 </file>
@@ -6220,14 +6301,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L367"/>
+  <dimension ref="A1:L365"/>
   <sheetFormatPr defaultColWidth="10.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.33203125" customWidth="1"/>
     <col min="2" max="2" width="41.5546875" customWidth="1"/>
     <col min="3" max="3" width="16.5546875" style="3" customWidth="1"/>
     <col min="4" max="5" width="16.5546875" customWidth="1"/>
-    <col min="6" max="6" width="29.5546875" customWidth="1"/>
+    <col min="6" max="6" width="29.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="33.77734375" customWidth="1"/>
     <col min="8" max="8" width="8.33203125" customWidth="1"/>
     <col min="9" max="9" width="7.77734375" customWidth="1"/>
@@ -6251,7 +6332,7 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -6517,11 +6598,11 @@
       <c r="E8" t="s">
         <v>692</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
+      <c r="F8" s="2" t="s">
+        <v>1951</v>
       </c>
       <c r="G8" t="s">
-        <v>1951</v>
+        <v>1945</v>
       </c>
       <c r="H8" t="s">
         <v>52</v>
@@ -6533,7 +6614,7 @@
         <v>1895</v>
       </c>
       <c r="K8" t="s">
-        <v>1952</v>
+        <v>1946</v>
       </c>
       <c r="L8" t="s">
         <v>1888</v>
@@ -6745,8 +6826,8 @@
       <c r="E14" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
+      <c r="F14" s="2" t="s">
+        <v>1952</v>
       </c>
       <c r="G14" t="s">
         <v>175</v>
@@ -7429,8 +7510,8 @@
       <c r="E32" t="s">
         <v>1893</v>
       </c>
-      <c r="F32" s="2">
-        <v>0</v>
+      <c r="F32" s="2" t="s">
+        <v>1976</v>
       </c>
       <c r="G32" t="s">
         <v>24</v>
@@ -7468,7 +7549,7 @@
         <v>692</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>190113840110</v>
       </c>
       <c r="G33" t="s">
         <v>164</v>
@@ -8493,8 +8574,8 @@
       <c r="E60" t="s">
         <v>23</v>
       </c>
-      <c r="F60" s="2">
-        <v>0</v>
+      <c r="F60" s="2" t="s">
+        <v>1953</v>
       </c>
       <c r="G60" t="s">
         <v>264</v>
@@ -9177,8 +9258,8 @@
       <c r="E78" t="s">
         <v>31</v>
       </c>
-      <c r="F78" s="2">
-        <v>0</v>
+      <c r="F78" s="2" t="s">
+        <v>1983</v>
       </c>
       <c r="G78" t="s">
         <v>325</v>
@@ -10733,7 +10814,7 @@
         <v>138</v>
       </c>
       <c r="E119" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F119" s="2">
         <v>22770205000199</v>
@@ -10887,8 +10968,8 @@
       <c r="E123" t="s">
         <v>31</v>
       </c>
-      <c r="F123" s="2">
-        <v>0</v>
+      <c r="F123" s="2" t="s">
+        <v>1954</v>
       </c>
       <c r="G123" t="s">
         <v>486</v>
@@ -11001,8 +11082,8 @@
       <c r="E126" t="s">
         <v>373</v>
       </c>
-      <c r="F126" s="2">
-        <v>0</v>
+      <c r="F126" s="2" t="s">
+        <v>1955</v>
       </c>
       <c r="G126" t="s">
         <v>500</v>
@@ -11039,8 +11120,8 @@
       <c r="E127" t="s">
         <v>1893</v>
       </c>
-      <c r="F127" s="2">
-        <v>0</v>
+      <c r="F127" s="2" t="s">
+        <v>1956</v>
       </c>
       <c r="G127" t="s">
         <v>16</v>
@@ -11113,7 +11194,7 @@
         <v>1227</v>
       </c>
       <c r="E129" t="s">
-        <v>1954</v>
+        <v>1948</v>
       </c>
       <c r="F129" s="2">
         <v>3637226000196</v>
@@ -11229,8 +11310,8 @@
       <c r="E132" t="s">
         <v>15</v>
       </c>
-      <c r="F132" s="2">
-        <v>0</v>
+      <c r="F132" s="2" t="s">
+        <v>1957</v>
       </c>
       <c r="G132" t="s">
         <v>519</v>
@@ -11495,8 +11576,8 @@
       <c r="E139" t="s">
         <v>78</v>
       </c>
-      <c r="F139" s="2">
-        <v>0</v>
+      <c r="F139" s="2" t="s">
+        <v>1958</v>
       </c>
       <c r="G139" t="s">
         <v>552</v>
@@ -11533,8 +11614,8 @@
       <c r="E140" t="s">
         <v>31</v>
       </c>
-      <c r="F140" s="2">
-        <v>0</v>
+      <c r="F140" s="2" t="s">
+        <v>1959</v>
       </c>
       <c r="G140" t="s">
         <v>556</v>
@@ -11571,8 +11652,8 @@
       <c r="E141" t="s">
         <v>63</v>
       </c>
-      <c r="F141" s="2">
-        <v>0</v>
+      <c r="F141" s="2" t="s">
+        <v>1960</v>
       </c>
       <c r="G141" t="s">
         <v>560</v>
@@ -11799,8 +11880,8 @@
       <c r="E147" t="s">
         <v>15</v>
       </c>
-      <c r="F147" s="2">
-        <v>0</v>
+      <c r="F147" s="2" t="s">
+        <v>1977</v>
       </c>
       <c r="G147" t="s">
         <v>583</v>
@@ -12331,8 +12412,8 @@
       <c r="E161" t="s">
         <v>692</v>
       </c>
-      <c r="F161" s="2">
-        <v>0</v>
+      <c r="F161" s="2" t="s">
+        <v>1961</v>
       </c>
       <c r="G161" t="s">
         <v>631</v>
@@ -12711,8 +12792,8 @@
       <c r="E171" t="s">
         <v>78</v>
       </c>
-      <c r="F171" s="2">
-        <v>0</v>
+      <c r="F171" s="2" t="s">
+        <v>1978</v>
       </c>
       <c r="G171" t="s">
         <v>673</v>
@@ -12749,8 +12830,8 @@
       <c r="E172" t="s">
         <v>15</v>
       </c>
-      <c r="F172" s="2">
-        <v>0</v>
+      <c r="F172" s="2" t="s">
+        <v>1962</v>
       </c>
       <c r="G172" t="s">
         <v>631</v>
@@ -12829,7 +12910,7 @@
         <v>685</v>
       </c>
       <c r="G174" t="s">
-        <v>1955</v>
+        <v>1949</v>
       </c>
       <c r="H174" t="s">
         <v>69</v>
@@ -12863,8 +12944,8 @@
       <c r="E175" t="s">
         <v>1901</v>
       </c>
-      <c r="F175" s="2">
-        <v>0</v>
+      <c r="F175" s="2" t="s">
+        <v>1963</v>
       </c>
       <c r="G175" t="s">
         <v>865</v>
@@ -12977,8 +13058,8 @@
       <c r="E178" t="s">
         <v>1893</v>
       </c>
-      <c r="F178" s="2">
-        <v>0</v>
+      <c r="F178" s="2" t="s">
+        <v>1979</v>
       </c>
       <c r="G178" t="s">
         <v>701</v>
@@ -13015,8 +13096,8 @@
       <c r="E179" t="s">
         <v>1900</v>
       </c>
-      <c r="F179" s="2">
-        <v>0</v>
+      <c r="F179" s="2" t="s">
+        <v>1964</v>
       </c>
       <c r="G179" t="s">
         <v>1902</v>
@@ -13127,7 +13208,7 @@
         <v>56</v>
       </c>
       <c r="E182" t="s">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>718</v>
@@ -14079,8 +14160,8 @@
       <c r="E207" t="s">
         <v>692</v>
       </c>
-      <c r="F207" s="2">
-        <v>0</v>
+      <c r="F207" s="2" t="s">
+        <v>1965</v>
       </c>
       <c r="G207" t="s">
         <v>457</v>
@@ -14117,8 +14198,8 @@
       <c r="E208" t="s">
         <v>31</v>
       </c>
-      <c r="F208" s="2">
-        <v>0</v>
+      <c r="F208" s="2" t="s">
+        <v>1966</v>
       </c>
       <c r="G208" t="s">
         <v>181</v>
@@ -14457,7 +14538,7 @@
         <v>56</v>
       </c>
       <c r="E217" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F217" s="2">
         <v>27093558000115</v>
@@ -14495,7 +14576,7 @@
         <v>56</v>
       </c>
       <c r="E218" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F218" s="2">
         <v>27093558000115</v>
@@ -14533,7 +14614,7 @@
         <v>56</v>
       </c>
       <c r="E219" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F219" s="2">
         <v>27093558000115</v>
@@ -14571,7 +14652,7 @@
         <v>56</v>
       </c>
       <c r="E220" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F220" s="2">
         <v>27093558000115</v>
@@ -14609,7 +14690,7 @@
         <v>56</v>
       </c>
       <c r="E221" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F221" s="2">
         <v>27093558000115</v>
@@ -14647,7 +14728,7 @@
         <v>56</v>
       </c>
       <c r="E222" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F222" s="2">
         <v>27093558000115</v>
@@ -14685,7 +14766,7 @@
         <v>56</v>
       </c>
       <c r="E223" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F223" s="2">
         <v>27093558000115</v>
@@ -14723,7 +14804,7 @@
         <v>56</v>
       </c>
       <c r="E224" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F224" s="2">
         <v>27093558000115</v>
@@ -14761,7 +14842,7 @@
         <v>56</v>
       </c>
       <c r="E225" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F225" s="2">
         <v>27093558000115</v>
@@ -14799,7 +14880,7 @@
         <v>56</v>
       </c>
       <c r="E226" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F226" s="2">
         <v>27093558000115</v>
@@ -14837,7 +14918,7 @@
         <v>56</v>
       </c>
       <c r="E227" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F227" s="2">
         <v>27093558000115</v>
@@ -14875,7 +14956,7 @@
         <v>56</v>
       </c>
       <c r="E228" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F228" s="2">
         <v>27093558000115</v>
@@ -14913,7 +14994,7 @@
         <v>106</v>
       </c>
       <c r="E229" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="F229" s="2">
         <v>27093558000115</v>
@@ -14953,8 +15034,8 @@
       <c r="E230" t="s">
         <v>373</v>
       </c>
-      <c r="F230" s="2">
-        <v>0</v>
+      <c r="F230" s="2" t="s">
+        <v>1967</v>
       </c>
       <c r="G230" t="s">
         <v>871</v>
@@ -15029,8 +15110,8 @@
       <c r="E232" t="s">
         <v>1901</v>
       </c>
-      <c r="F232" s="2">
-        <v>0</v>
+      <c r="F232" s="2" t="s">
+        <v>1968</v>
       </c>
       <c r="G232" t="s">
         <v>880</v>
@@ -15067,8 +15148,8 @@
       <c r="E233" t="s">
         <v>1893</v>
       </c>
-      <c r="F233" s="2">
-        <v>0</v>
+      <c r="F233" s="2" t="s">
+        <v>1969</v>
       </c>
       <c r="G233" t="s">
         <v>122</v>
@@ -15181,8 +15262,8 @@
       <c r="E236" t="s">
         <v>1893</v>
       </c>
-      <c r="F236" s="2">
-        <v>0</v>
+      <c r="F236" s="2" t="s">
+        <v>1970</v>
       </c>
       <c r="G236" t="s">
         <v>32</v>
@@ -15395,78 +15476,78 @@
     </row>
     <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1944</v>
+        <v>912</v>
       </c>
       <c r="B242" t="s">
-        <v>1944</v>
+        <v>913</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="D242" t="s">
         <v>56</v>
       </c>
       <c r="E242" t="s">
-        <v>1945</v>
+        <v>15</v>
       </c>
       <c r="F242" s="2">
-        <v>0</v>
+        <v>29060647001758</v>
       </c>
       <c r="G242" t="s">
-        <v>1946</v>
+        <v>1904</v>
       </c>
       <c r="H242" t="s">
-        <v>39</v>
+        <v>243</v>
       </c>
       <c r="I242">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J242">
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>1947</v>
+        <v>914</v>
       </c>
       <c r="L242" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1948</v>
+        <v>912</v>
       </c>
       <c r="B243" t="s">
-        <v>1948</v>
+        <v>915</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>55</v>
+        <v>476</v>
       </c>
       <c r="D243" t="s">
-        <v>684</v>
+        <v>56</v>
       </c>
       <c r="E243" t="s">
-        <v>1945</v>
+        <v>15</v>
       </c>
       <c r="F243" s="2">
-        <v>0</v>
+        <v>29060647001758</v>
       </c>
       <c r="G243" t="s">
-        <v>482</v>
+        <v>916</v>
       </c>
       <c r="H243" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="I243">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J243">
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>1949</v>
+        <v>917</v>
       </c>
       <c r="L243" t="s">
-        <v>1887</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15474,10 +15555,10 @@
         <v>912</v>
       </c>
       <c r="B244" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>96</v>
+        <v>353</v>
       </c>
       <c r="D244" t="s">
         <v>56</v>
@@ -15489,19 +15570,19 @@
         <v>29060647001758</v>
       </c>
       <c r="G244" t="s">
-        <v>1904</v>
+        <v>242</v>
       </c>
       <c r="H244" t="s">
         <v>243</v>
       </c>
       <c r="I244">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J244">
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="L244" t="s">
         <v>1886</v>
@@ -15509,75 +15590,75 @@
     </row>
     <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="B245" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>476</v>
+        <v>137</v>
       </c>
       <c r="D245" t="s">
         <v>56</v>
       </c>
       <c r="E245" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="F245" s="2">
-        <v>29060647001758</v>
+        <v>22060255000182</v>
       </c>
       <c r="G245" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="H245" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="I245">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J245">
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="L245" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="B246" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>353</v>
+        <v>481</v>
       </c>
       <c r="D246" t="s">
-        <v>56</v>
+        <v>476</v>
       </c>
       <c r="E246" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F246" s="2">
-        <v>29060647001758</v>
+        <v>71304687001845</v>
       </c>
       <c r="G246" t="s">
-        <v>242</v>
+        <v>926</v>
       </c>
       <c r="H246" t="s">
-        <v>243</v>
+        <v>17</v>
       </c>
       <c r="I246">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J246">
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="L246" t="s">
         <v>1886</v>
@@ -15585,40 +15666,40 @@
     </row>
     <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B247" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>137</v>
+        <v>929</v>
       </c>
       <c r="D247" t="s">
-        <v>56</v>
+        <v>476</v>
       </c>
       <c r="E247" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="F247" s="2">
-        <v>22060255000182</v>
+        <v>71304687005832</v>
       </c>
       <c r="G247" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="H247" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I247">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J247">
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="L247" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15626,34 +15707,34 @@
         <v>924</v>
       </c>
       <c r="B248" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>481</v>
+        <v>46</v>
       </c>
       <c r="D248" t="s">
-        <v>476</v>
+        <v>359</v>
       </c>
       <c r="E248" t="s">
         <v>31</v>
       </c>
       <c r="F248" s="2">
-        <v>71304687001845</v>
+        <v>71304687000105</v>
       </c>
       <c r="G248" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="H248" t="s">
         <v>17</v>
       </c>
       <c r="I248">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J248">
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="L248" t="s">
         <v>1886</v>
@@ -15664,148 +15745,148 @@
         <v>924</v>
       </c>
       <c r="B249" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>929</v>
+        <v>481</v>
       </c>
       <c r="D249" t="s">
-        <v>476</v>
+        <v>22</v>
       </c>
       <c r="E249" t="s">
         <v>31</v>
       </c>
       <c r="F249" s="2">
-        <v>71304687005832</v>
+        <v>71304687002817</v>
       </c>
       <c r="G249" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="H249" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I249">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J249">
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="L249" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>924</v>
+        <v>938</v>
       </c>
       <c r="B250" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>46</v>
+        <v>476</v>
       </c>
       <c r="D250" t="s">
-        <v>359</v>
+        <v>56</v>
       </c>
       <c r="E250" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F250" s="2">
-        <v>71304687000105</v>
+        <v>9627249000104</v>
       </c>
       <c r="G250" t="s">
-        <v>933</v>
+        <v>1905</v>
       </c>
       <c r="H250" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I250">
-        <v>30</v>
-      </c>
-      <c r="J250">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J250" t="s">
+        <v>1896</v>
       </c>
       <c r="K250" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="L250" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>924</v>
+        <v>941</v>
       </c>
       <c r="B251" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>481</v>
+        <v>305</v>
       </c>
       <c r="D251" t="s">
         <v>22</v>
       </c>
       <c r="E251" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F251" s="2">
-        <v>71304687002817</v>
+        <v>31849857000104</v>
       </c>
       <c r="G251" t="s">
-        <v>936</v>
+        <v>405</v>
       </c>
       <c r="H251" t="s">
-        <v>17</v>
+        <v>270</v>
       </c>
       <c r="I251">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J251">
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="L251" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="B252" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>476</v>
+        <v>1883</v>
       </c>
       <c r="D252" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E252" t="s">
-        <v>115</v>
-      </c>
-      <c r="F252" s="2">
-        <v>9627249000104</v>
+        <v>1901</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>1971</v>
       </c>
       <c r="G252" t="s">
-        <v>1905</v>
+        <v>946</v>
       </c>
       <c r="H252" t="s">
         <v>52</v>
       </c>
       <c r="I252">
-        <v>2</v>
-      </c>
-      <c r="J252" t="s">
-        <v>1896</v>
+        <v>5</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="L252" t="s">
         <v>1888</v>
@@ -15813,37 +15894,37 @@
     </row>
     <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B253" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>305</v>
+        <v>29</v>
       </c>
       <c r="D253" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E253" t="s">
-        <v>115</v>
-      </c>
-      <c r="F253" s="2">
-        <v>31849857000104</v>
+        <v>1901</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>1971</v>
       </c>
       <c r="G253" t="s">
-        <v>405</v>
+        <v>865</v>
       </c>
       <c r="H253" t="s">
-        <v>270</v>
+        <v>39</v>
       </c>
       <c r="I253">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J253">
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="L253" t="s">
         <v>1887</v>
@@ -15854,37 +15935,37 @@
         <v>944</v>
       </c>
       <c r="B254" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1883</v>
+        <v>275</v>
       </c>
       <c r="D254" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E254" t="s">
         <v>1901</v>
       </c>
       <c r="F254" s="2">
-        <v>0</v>
+        <v>21752910000109</v>
       </c>
       <c r="G254" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="H254" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="I254">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="J254">
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="L254" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15892,186 +15973,186 @@
         <v>944</v>
       </c>
       <c r="B255" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="C255" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="D255" t="s">
+        <v>77</v>
+      </c>
+      <c r="E255" t="s">
+        <v>78</v>
+      </c>
+      <c r="F255" s="2">
+        <v>21752910000109</v>
+      </c>
+      <c r="G255" t="s">
+        <v>954</v>
+      </c>
+      <c r="H255" t="s">
+        <v>52</v>
+      </c>
+      <c r="I255">
         <v>29</v>
       </c>
-      <c r="D255" t="s">
-        <v>56</v>
-      </c>
-      <c r="E255" t="s">
-        <v>1901</v>
-      </c>
-      <c r="F255" s="2">
-        <v>0</v>
-      </c>
-      <c r="G255" t="s">
-        <v>865</v>
-      </c>
-      <c r="H255" t="s">
-        <v>39</v>
-      </c>
-      <c r="I255">
-        <v>6</v>
-      </c>
       <c r="J255">
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="L255" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="256" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="B256" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="D256" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="E256" t="s">
-        <v>1901</v>
+        <v>63</v>
       </c>
       <c r="F256" s="2">
-        <v>21752910000109</v>
+        <v>86960945000170</v>
       </c>
       <c r="G256" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="H256" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="I256">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J256">
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="L256" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="257" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>944</v>
+        <v>960</v>
       </c>
       <c r="B257" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>624</v>
+        <v>494</v>
       </c>
       <c r="D257" t="s">
         <v>77</v>
       </c>
       <c r="E257" t="s">
-        <v>78</v>
-      </c>
-      <c r="F257" s="2">
-        <v>21752910000109</v>
+        <v>1901</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>962</v>
       </c>
       <c r="G257" t="s">
-        <v>954</v>
+        <v>427</v>
       </c>
       <c r="H257" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I257">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J257">
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="L257" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="258" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="B258" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="D258" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="E258" t="s">
         <v>63</v>
       </c>
       <c r="F258" s="2">
-        <v>86960945000170</v>
+        <v>45129340000155</v>
       </c>
       <c r="G258" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="H258" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="I258">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J258">
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="L258" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="259" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="B259" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>494</v>
+        <v>133</v>
       </c>
       <c r="D259" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="E259" t="s">
-        <v>1901</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>962</v>
+        <v>115</v>
+      </c>
+      <c r="F259" s="2">
+        <v>26251982000188</v>
       </c>
       <c r="G259" t="s">
-        <v>427</v>
+        <v>242</v>
       </c>
       <c r="H259" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="I259">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="J259">
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="L259" t="s">
         <v>1886</v>
@@ -16079,116 +16160,116 @@
     </row>
     <row r="260" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="B260" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D260" t="s">
         <v>56</v>
       </c>
       <c r="E260" t="s">
-        <v>63</v>
+        <v>768</v>
       </c>
       <c r="F260" s="2">
-        <v>45129340000155</v>
+        <v>10158592000128</v>
       </c>
       <c r="G260" t="s">
-        <v>966</v>
+        <v>1906</v>
       </c>
       <c r="H260" t="s">
-        <v>69</v>
+        <v>973</v>
       </c>
       <c r="I260">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J260">
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="L260" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="261" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="B261" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>133</v>
+        <v>1885</v>
       </c>
       <c r="D261" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E261" t="s">
-        <v>115</v>
-      </c>
-      <c r="F261" s="2">
-        <v>26251982000188</v>
+        <v>31</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>1980</v>
       </c>
       <c r="G261" t="s">
-        <v>242</v>
+        <v>977</v>
       </c>
       <c r="H261" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="I261">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J261">
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="L261" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="262" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="B262" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>37</v>
+        <v>481</v>
       </c>
       <c r="D262" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E262" t="s">
-        <v>768</v>
+        <v>31</v>
       </c>
       <c r="F262" s="2">
-        <v>10158592000128</v>
+        <v>8070508000330</v>
       </c>
       <c r="G262" t="s">
-        <v>1906</v>
+        <v>980</v>
       </c>
       <c r="H262" t="s">
-        <v>973</v>
+        <v>17</v>
       </c>
       <c r="I262">
-        <v>2</v>
-      </c>
-      <c r="J262">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="J262" t="s">
+        <v>1897</v>
       </c>
       <c r="K262" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="L262" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="263" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16196,37 +16277,37 @@
         <v>975</v>
       </c>
       <c r="B263" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>1885</v>
+        <v>481</v>
       </c>
       <c r="D263" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E263" t="s">
-        <v>31</v>
+        <v>1884</v>
       </c>
       <c r="F263" s="2">
-        <v>0</v>
+        <v>8070508008314</v>
       </c>
       <c r="G263" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="H263" t="s">
-        <v>285</v>
+        <v>17</v>
       </c>
       <c r="I263">
-        <v>1</v>
-      </c>
-      <c r="J263">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="J263" t="s">
+        <v>1897</v>
       </c>
       <c r="K263" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="L263" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="264" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16234,34 +16315,34 @@
         <v>975</v>
       </c>
       <c r="B264" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>481</v>
+        <v>731</v>
       </c>
       <c r="D264" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
       <c r="E264" t="s">
         <v>31</v>
       </c>
       <c r="F264" s="2">
-        <v>8070508000330</v>
+        <v>8070508002707</v>
       </c>
       <c r="G264" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="H264" t="s">
         <v>17</v>
       </c>
       <c r="I264">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="J264" t="s">
         <v>1897</v>
       </c>
       <c r="K264" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="L264" t="s">
         <v>1886</v>
@@ -16272,37 +16353,37 @@
         <v>975</v>
       </c>
       <c r="B265" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>481</v>
+        <v>648</v>
       </c>
       <c r="D265" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="E265" t="s">
-        <v>1884</v>
+        <v>31</v>
       </c>
       <c r="F265" s="2">
-        <v>8070508008314</v>
+        <v>8070508000178</v>
       </c>
       <c r="G265" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="H265" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I265">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J265" t="s">
         <v>1897</v>
       </c>
       <c r="K265" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="L265" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="266" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16310,34 +16391,34 @@
         <v>975</v>
       </c>
       <c r="B266" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>731</v>
+        <v>1227</v>
       </c>
       <c r="D266" t="s">
-        <v>306</v>
+        <v>56</v>
       </c>
       <c r="E266" t="s">
         <v>31</v>
       </c>
       <c r="F266" s="2">
-        <v>8070508002707</v>
+        <v>8070508000178</v>
       </c>
       <c r="G266" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="H266" t="s">
         <v>17</v>
       </c>
       <c r="I266">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="J266" t="s">
         <v>1897</v>
       </c>
       <c r="K266" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="L266" t="s">
         <v>1886</v>
@@ -16348,13 +16429,13 @@
         <v>975</v>
       </c>
       <c r="B267" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>648</v>
+        <v>481</v>
       </c>
       <c r="D267" t="s">
-        <v>47</v>
+        <v>494</v>
       </c>
       <c r="E267" t="s">
         <v>31</v>
@@ -16363,22 +16444,22 @@
         <v>8070508000178</v>
       </c>
       <c r="G267" t="s">
-        <v>989</v>
+        <v>430</v>
       </c>
       <c r="H267" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I267">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="J267" t="s">
         <v>1897</v>
       </c>
       <c r="K267" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="L267" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="268" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16386,34 +16467,34 @@
         <v>975</v>
       </c>
       <c r="B268" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>1227</v>
+        <v>997</v>
       </c>
       <c r="D268" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E268" t="s">
-        <v>31</v>
+        <v>1884</v>
       </c>
       <c r="F268" s="2">
-        <v>8070508000178</v>
+        <v>8070508012184</v>
       </c>
       <c r="G268" t="s">
-        <v>992</v>
+        <v>388</v>
       </c>
       <c r="H268" t="s">
         <v>17</v>
       </c>
       <c r="I268">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J268" t="s">
         <v>1897</v>
       </c>
       <c r="K268" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="L268" t="s">
         <v>1886</v>
@@ -16424,34 +16505,34 @@
         <v>975</v>
       </c>
       <c r="B269" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>481</v>
       </c>
       <c r="D269" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E269" t="s">
         <v>31</v>
       </c>
       <c r="F269" s="2">
-        <v>8070508000178</v>
+        <v>8070508006613</v>
       </c>
       <c r="G269" t="s">
-        <v>430</v>
+        <v>144</v>
       </c>
       <c r="H269" t="s">
         <v>17</v>
       </c>
       <c r="I269">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J269" t="s">
         <v>1897</v>
       </c>
       <c r="K269" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="L269" t="s">
         <v>1886</v>
@@ -16462,10 +16543,10 @@
         <v>975</v>
       </c>
       <c r="B270" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="D270" t="s">
         <v>29</v>
@@ -16474,22 +16555,22 @@
         <v>1884</v>
       </c>
       <c r="F270" s="2">
-        <v>8070508012184</v>
+        <v>8070508009558</v>
       </c>
       <c r="G270" t="s">
-        <v>388</v>
+        <v>591</v>
       </c>
       <c r="H270" t="s">
         <v>17</v>
       </c>
       <c r="I270">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J270" t="s">
         <v>1897</v>
       </c>
       <c r="K270" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="L270" t="s">
         <v>1886</v>
@@ -16500,34 +16581,34 @@
         <v>975</v>
       </c>
       <c r="B271" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>481</v>
+        <v>342</v>
       </c>
       <c r="D271" t="s">
-        <v>490</v>
+        <v>56</v>
       </c>
       <c r="E271" t="s">
         <v>31</v>
       </c>
       <c r="F271" s="2">
-        <v>8070508006613</v>
+        <v>8070508000178</v>
       </c>
       <c r="G271" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="H271" t="s">
         <v>17</v>
       </c>
       <c r="I271">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J271" t="s">
         <v>1897</v>
       </c>
       <c r="K271" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="L271" t="s">
         <v>1886</v>
@@ -16538,37 +16619,37 @@
         <v>975</v>
       </c>
       <c r="B272" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>1002</v>
+        <v>342</v>
       </c>
       <c r="D272" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E272" t="s">
-        <v>1884</v>
+        <v>31</v>
       </c>
       <c r="F272" s="2">
-        <v>8070508009558</v>
+        <v>8070508000178</v>
       </c>
       <c r="G272" t="s">
-        <v>591</v>
+        <v>1007</v>
       </c>
       <c r="H272" t="s">
-        <v>17</v>
+        <v>973</v>
       </c>
       <c r="I272">
-        <v>2</v>
-      </c>
-      <c r="J272" t="s">
-        <v>1897</v>
+        <v>1</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
       </c>
       <c r="K272" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="L272" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="273" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16576,34 +16657,34 @@
         <v>975</v>
       </c>
       <c r="B273" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>342</v>
+        <v>46</v>
       </c>
       <c r="D273" t="s">
-        <v>56</v>
+        <v>1883</v>
       </c>
       <c r="E273" t="s">
         <v>31</v>
       </c>
       <c r="F273" s="2">
-        <v>8070508000178</v>
+        <v>8070508006885</v>
       </c>
       <c r="G273" t="s">
-        <v>111</v>
+        <v>714</v>
       </c>
       <c r="H273" t="s">
         <v>17</v>
       </c>
       <c r="I273">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J273" t="s">
         <v>1897</v>
       </c>
       <c r="K273" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="L273" t="s">
         <v>1886</v>
@@ -16614,37 +16695,37 @@
         <v>975</v>
       </c>
       <c r="B274" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>342</v>
+        <v>648</v>
       </c>
       <c r="D274" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E274" t="s">
         <v>31</v>
       </c>
       <c r="F274" s="2">
-        <v>8070508000178</v>
+        <v>8070508006966</v>
       </c>
       <c r="G274" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="H274" t="s">
-        <v>973</v>
+        <v>17</v>
       </c>
       <c r="I274">
-        <v>1</v>
-      </c>
-      <c r="J274">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="J274" t="s">
+        <v>1897</v>
       </c>
       <c r="K274" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="L274" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="275" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16652,37 +16733,37 @@
         <v>975</v>
       </c>
       <c r="B275" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>46</v>
+        <v>741</v>
       </c>
       <c r="D275" t="s">
-        <v>1883</v>
+        <v>180</v>
       </c>
       <c r="E275" t="s">
-        <v>31</v>
+        <v>1884</v>
       </c>
       <c r="F275" s="2">
-        <v>8070508006885</v>
+        <v>8070508016767</v>
       </c>
       <c r="G275" t="s">
-        <v>714</v>
+        <v>1015</v>
       </c>
       <c r="H275" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="I275">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="J275" t="s">
         <v>1897</v>
       </c>
       <c r="K275" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="L275" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="276" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16690,34 +16771,34 @@
         <v>975</v>
       </c>
       <c r="B276" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>648</v>
       </c>
       <c r="D276" t="s">
-        <v>77</v>
+        <v>1881</v>
       </c>
       <c r="E276" t="s">
         <v>31</v>
       </c>
       <c r="F276" s="2">
-        <v>8070508006966</v>
+        <v>8070508012427</v>
       </c>
       <c r="G276" t="s">
-        <v>1012</v>
+        <v>787</v>
       </c>
       <c r="H276" t="s">
         <v>17</v>
       </c>
       <c r="I276">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J276" t="s">
         <v>1897</v>
       </c>
       <c r="K276" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="L276" t="s">
         <v>1886</v>
@@ -16728,37 +16809,37 @@
         <v>975</v>
       </c>
       <c r="B277" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>741</v>
+        <v>1020</v>
       </c>
       <c r="D277" t="s">
-        <v>180</v>
+        <v>359</v>
       </c>
       <c r="E277" t="s">
-        <v>1884</v>
+        <v>31</v>
       </c>
       <c r="F277" s="2">
-        <v>8070508016767</v>
+        <v>8070508000178</v>
       </c>
       <c r="G277" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="H277" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="I277">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="J277" t="s">
         <v>1897</v>
       </c>
       <c r="K277" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="L277" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="278" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16766,34 +16847,34 @@
         <v>975</v>
       </c>
       <c r="B278" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>648</v>
+        <v>481</v>
       </c>
       <c r="D278" t="s">
-        <v>1881</v>
+        <v>342</v>
       </c>
       <c r="E278" t="s">
-        <v>31</v>
+        <v>1884</v>
       </c>
       <c r="F278" s="2">
-        <v>8070508012427</v>
+        <v>8070508015876</v>
       </c>
       <c r="G278" t="s">
-        <v>787</v>
+        <v>1024</v>
       </c>
       <c r="H278" t="s">
         <v>17</v>
       </c>
       <c r="I278">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J278" t="s">
         <v>1897</v>
       </c>
       <c r="K278" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="L278" t="s">
         <v>1886</v>
@@ -16804,13 +16885,13 @@
         <v>975</v>
       </c>
       <c r="B279" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>1020</v>
+        <v>1881</v>
       </c>
       <c r="D279" t="s">
-        <v>359</v>
+        <v>30</v>
       </c>
       <c r="E279" t="s">
         <v>31</v>
@@ -16819,22 +16900,22 @@
         <v>8070508000178</v>
       </c>
       <c r="G279" t="s">
-        <v>1021</v>
+        <v>482</v>
       </c>
       <c r="H279" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I279">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="J279" t="s">
         <v>1897</v>
       </c>
       <c r="K279" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="L279" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="280" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16842,34 +16923,34 @@
         <v>975</v>
       </c>
       <c r="B280" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>481</v>
+        <v>275</v>
       </c>
       <c r="D280" t="s">
-        <v>342</v>
+        <v>29</v>
       </c>
       <c r="E280" t="s">
         <v>1884</v>
       </c>
       <c r="F280" s="2">
-        <v>8070508015876</v>
+        <v>8070508015795</v>
       </c>
       <c r="G280" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="H280" t="s">
         <v>17</v>
       </c>
       <c r="I280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J280" t="s">
         <v>1897</v>
       </c>
       <c r="K280" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="L280" t="s">
         <v>1886</v>
@@ -16880,37 +16961,37 @@
         <v>975</v>
       </c>
       <c r="B281" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>1881</v>
+        <v>481</v>
       </c>
       <c r="D281" t="s">
-        <v>30</v>
+        <v>494</v>
       </c>
       <c r="E281" t="s">
-        <v>31</v>
+        <v>1884</v>
       </c>
       <c r="F281" s="2">
         <v>8070508000178</v>
       </c>
       <c r="G281" t="s">
-        <v>482</v>
+        <v>1032</v>
       </c>
       <c r="H281" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I281">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="J281" t="s">
         <v>1897</v>
       </c>
       <c r="K281" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="L281" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="282" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16918,22 +16999,22 @@
         <v>975</v>
       </c>
       <c r="B282" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>275</v>
+        <v>157</v>
       </c>
       <c r="D282" t="s">
-        <v>29</v>
+        <v>359</v>
       </c>
       <c r="E282" t="s">
-        <v>1884</v>
+        <v>31</v>
       </c>
       <c r="F282" s="2">
-        <v>8070508015795</v>
+        <v>8070508012508</v>
       </c>
       <c r="G282" t="s">
-        <v>1029</v>
+        <v>346</v>
       </c>
       <c r="H282" t="s">
         <v>17</v>
@@ -16945,7 +17026,7 @@
         <v>1897</v>
       </c>
       <c r="K282" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="L282" t="s">
         <v>1886</v>
@@ -16956,34 +17037,34 @@
         <v>975</v>
       </c>
       <c r="B283" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>481</v>
       </c>
       <c r="D283" t="s">
-        <v>494</v>
+        <v>77</v>
       </c>
       <c r="E283" t="s">
-        <v>1884</v>
+        <v>31</v>
       </c>
       <c r="F283" s="2">
-        <v>8070508000178</v>
+        <v>8070508006702</v>
       </c>
       <c r="G283" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="H283" t="s">
         <v>17</v>
       </c>
       <c r="I283">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="J283" t="s">
         <v>1897</v>
       </c>
       <c r="K283" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="L283" t="s">
         <v>1886</v>
@@ -16994,34 +17075,34 @@
         <v>975</v>
       </c>
       <c r="B284" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>157</v>
+        <v>1040</v>
       </c>
       <c r="D284" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E284" t="s">
         <v>31</v>
       </c>
       <c r="F284" s="2">
-        <v>8070508012508</v>
+        <v>8070508000178</v>
       </c>
       <c r="G284" t="s">
-        <v>346</v>
+        <v>1041</v>
       </c>
       <c r="H284" t="s">
         <v>17</v>
       </c>
       <c r="I284">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J284" t="s">
         <v>1897</v>
       </c>
       <c r="K284" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="L284" t="s">
         <v>1886</v>
@@ -17032,34 +17113,34 @@
         <v>975</v>
       </c>
       <c r="B285" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>481</v>
+        <v>648</v>
       </c>
       <c r="D285" t="s">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="E285" t="s">
-        <v>31</v>
+        <v>1884</v>
       </c>
       <c r="F285" s="2">
-        <v>8070508006702</v>
+        <v>8070508016414</v>
       </c>
       <c r="G285" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="H285" t="s">
         <v>17</v>
       </c>
       <c r="I285">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J285" t="s">
         <v>1897</v>
       </c>
       <c r="K285" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="L285" t="s">
         <v>1886</v>
@@ -17067,37 +17148,37 @@
     </row>
     <row r="286" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>975</v>
+        <v>1046</v>
       </c>
       <c r="B286" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>1040</v>
+        <v>306</v>
       </c>
       <c r="D286" t="s">
-        <v>306</v>
+        <v>30</v>
       </c>
       <c r="E286" t="s">
         <v>31</v>
       </c>
-      <c r="F286" s="2">
-        <v>8070508000178</v>
+      <c r="F286" s="2" t="s">
+        <v>1981</v>
       </c>
       <c r="G286" t="s">
-        <v>1041</v>
+        <v>170</v>
       </c>
       <c r="H286" t="s">
         <v>17</v>
       </c>
       <c r="I286">
-        <v>24</v>
-      </c>
-      <c r="J286" t="s">
-        <v>1897</v>
+        <v>2</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
       </c>
       <c r="K286" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="L286" t="s">
         <v>1886</v>
@@ -17105,116 +17186,116 @@
     </row>
     <row r="287" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>975</v>
+        <v>1049</v>
       </c>
       <c r="B287" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>648</v>
+        <v>1881</v>
       </c>
       <c r="D287" t="s">
-        <v>359</v>
+        <v>30</v>
       </c>
       <c r="E287" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F287" s="2">
-        <v>8070508016414</v>
+        <v>1901</v>
+      </c>
+      <c r="F287" s="2" t="s">
+        <v>1972</v>
       </c>
       <c r="G287" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="H287" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="I287">
-        <v>35</v>
-      </c>
-      <c r="J287" t="s">
-        <v>1897</v>
+        <v>1</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
       </c>
       <c r="K287" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="L287" t="s">
-        <v>1886</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="288" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="B288" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>306</v>
+        <v>126</v>
       </c>
       <c r="D288" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E288" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F288" s="2">
-        <v>0</v>
+        <v>10466983000100</v>
       </c>
       <c r="G288" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="H288" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="I288">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J288">
         <v>0</v>
       </c>
       <c r="K288" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="L288" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="289" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B289" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>1881</v>
+        <v>13</v>
       </c>
       <c r="D289" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E289" t="s">
-        <v>1901</v>
+        <v>115</v>
       </c>
       <c r="F289" s="2">
-        <v>0</v>
+        <v>10466983000100</v>
       </c>
       <c r="G289" t="s">
-        <v>1051</v>
+        <v>846</v>
       </c>
       <c r="H289" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="I289">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J289">
         <v>0</v>
       </c>
       <c r="K289" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="L289" t="s">
-        <v>1892</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="290" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17222,10 +17303,10 @@
         <v>1053</v>
       </c>
       <c r="B290" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="D290" t="s">
         <v>56</v>
@@ -17237,19 +17318,19 @@
         <v>10466983000100</v>
       </c>
       <c r="G290" t="s">
-        <v>116</v>
+        <v>1059</v>
       </c>
       <c r="H290" t="s">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="I290">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J290">
         <v>0</v>
       </c>
       <c r="K290" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="L290" t="s">
         <v>1888</v>
@@ -17260,13 +17341,13 @@
         <v>1053</v>
       </c>
       <c r="B291" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="D291" t="s">
-        <v>56</v>
+        <v>379</v>
       </c>
       <c r="E291" t="s">
         <v>115</v>
@@ -17275,19 +17356,19 @@
         <v>10466983000100</v>
       </c>
       <c r="G291" t="s">
-        <v>846</v>
+        <v>1905</v>
       </c>
       <c r="H291" t="s">
         <v>52</v>
       </c>
       <c r="I291">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J291">
         <v>0</v>
       </c>
       <c r="K291" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="L291" t="s">
         <v>1888</v>
@@ -17295,37 +17376,37 @@
     </row>
     <row r="292" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1053</v>
+        <v>1063</v>
       </c>
       <c r="B292" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>13</v>
+        <v>662</v>
       </c>
       <c r="D292" t="s">
-        <v>56</v>
+        <v>379</v>
       </c>
       <c r="E292" t="s">
-        <v>115</v>
+        <v>1901</v>
       </c>
       <c r="F292" s="2">
-        <v>10466983000100</v>
+        <v>4882166000725</v>
       </c>
       <c r="G292" t="s">
-        <v>1059</v>
+        <v>663</v>
       </c>
       <c r="H292" t="s">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="I292">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J292">
         <v>0</v>
       </c>
       <c r="K292" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="L292" t="s">
         <v>1888</v>
@@ -17333,28 +17414,28 @@
     </row>
     <row r="293" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1053</v>
+        <v>1066</v>
       </c>
       <c r="B293" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>126</v>
+        <v>476</v>
       </c>
       <c r="D293" t="s">
-        <v>379</v>
+        <v>56</v>
       </c>
       <c r="E293" t="s">
-        <v>115</v>
+        <v>1068</v>
       </c>
       <c r="F293" s="2">
-        <v>10466983000100</v>
+        <v>7382924000149</v>
       </c>
       <c r="G293" t="s">
-        <v>1905</v>
+        <v>1069</v>
       </c>
       <c r="H293" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="I293">
         <v>6</v>
@@ -17363,45 +17444,45 @@
         <v>0</v>
       </c>
       <c r="K293" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="L293" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="294" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="B294" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>662</v>
+        <v>472</v>
       </c>
       <c r="D294" t="s">
-        <v>379</v>
+        <v>56</v>
       </c>
       <c r="E294" t="s">
-        <v>1901</v>
+        <v>1068</v>
       </c>
       <c r="F294" s="2">
-        <v>4882166000725</v>
+        <v>3771834000199</v>
       </c>
       <c r="G294" t="s">
-        <v>663</v>
+        <v>1073</v>
       </c>
       <c r="H294" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="I294">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J294">
         <v>0</v>
       </c>
       <c r="K294" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="L294" t="s">
         <v>1888</v>
@@ -17409,265 +17490,265 @@
     </row>
     <row r="295" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
       <c r="B295" t="s">
-        <v>1067</v>
+        <v>1076</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>476</v>
+        <v>1077</v>
       </c>
       <c r="D295" t="s">
         <v>56</v>
       </c>
       <c r="E295" t="s">
-        <v>1068</v>
+        <v>495</v>
       </c>
       <c r="F295" s="2">
-        <v>7382924000149</v>
+        <v>9491435000150</v>
       </c>
       <c r="G295" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="H295" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="I295">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J295">
         <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="L295" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="296" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
       <c r="B296" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>472</v>
+        <v>349</v>
       </c>
       <c r="D296" t="s">
-        <v>56</v>
+        <v>359</v>
       </c>
       <c r="E296" t="s">
-        <v>1068</v>
+        <v>1082</v>
       </c>
       <c r="F296" s="2">
-        <v>3771834000199</v>
+        <v>10975945000263</v>
       </c>
       <c r="G296" t="s">
-        <v>1073</v>
+        <v>239</v>
       </c>
       <c r="H296" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I296">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J296">
         <v>0</v>
       </c>
       <c r="K296" t="s">
-        <v>1074</v>
+        <v>1083</v>
       </c>
       <c r="L296" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="297" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1075</v>
+        <v>1084</v>
       </c>
       <c r="B297" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>1077</v>
+        <v>143</v>
       </c>
       <c r="D297" t="s">
         <v>56</v>
       </c>
       <c r="E297" t="s">
-        <v>495</v>
+        <v>115</v>
       </c>
       <c r="F297" s="2">
-        <v>9491435000150</v>
+        <v>89082085000450</v>
       </c>
       <c r="G297" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="H297" t="s">
-        <v>17</v>
+        <v>233</v>
       </c>
       <c r="I297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J297">
         <v>0</v>
       </c>
       <c r="K297" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="L297" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="298" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="B298" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>349</v>
+        <v>1883</v>
       </c>
       <c r="D298" t="s">
-        <v>359</v>
+        <v>30</v>
       </c>
       <c r="E298" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F298" s="2">
-        <v>10975945000263</v>
+        <v>115</v>
+      </c>
+      <c r="F298" s="2" t="s">
+        <v>1973</v>
       </c>
       <c r="G298" t="s">
-        <v>239</v>
+        <v>468</v>
       </c>
       <c r="H298" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I298">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J298">
         <v>0</v>
       </c>
       <c r="K298" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="L298" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="299" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B299" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>143</v>
+        <v>372</v>
       </c>
       <c r="D299" t="s">
-        <v>56</v>
+        <v>476</v>
       </c>
       <c r="E299" t="s">
         <v>115</v>
       </c>
       <c r="F299" s="2">
-        <v>89082085000450</v>
+        <v>12898928000160</v>
       </c>
       <c r="G299" t="s">
-        <v>1086</v>
+        <v>865</v>
       </c>
       <c r="H299" t="s">
-        <v>233</v>
+        <v>39</v>
       </c>
       <c r="I299">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J299">
         <v>0</v>
       </c>
       <c r="K299" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="L299" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="300" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="B300" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>1883</v>
+        <v>1095</v>
       </c>
       <c r="D300" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E300" t="s">
         <v>115</v>
       </c>
       <c r="F300" s="2">
-        <v>0</v>
+        <v>19238174000115</v>
       </c>
       <c r="G300" t="s">
-        <v>468</v>
+        <v>876</v>
       </c>
       <c r="H300" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I300">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J300">
         <v>0</v>
       </c>
       <c r="K300" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="L300" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="301" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="B301" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>372</v>
+        <v>14</v>
       </c>
       <c r="D301" t="s">
-        <v>476</v>
+        <v>56</v>
       </c>
       <c r="E301" t="s">
         <v>115</v>
       </c>
       <c r="F301" s="2">
-        <v>12898928000160</v>
+        <v>2799488000194</v>
       </c>
       <c r="G301" t="s">
-        <v>865</v>
+        <v>396</v>
       </c>
       <c r="H301" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I301">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J301">
         <v>0</v>
       </c>
       <c r="K301" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="L301" t="s">
         <v>1887</v>
@@ -17675,151 +17756,151 @@
     </row>
     <row r="302" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="B302" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>1095</v>
+        <v>185</v>
       </c>
       <c r="D302" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E302" t="s">
-        <v>115</v>
-      </c>
-      <c r="F302" s="2">
-        <v>19238174000115</v>
+        <v>1901</v>
+      </c>
+      <c r="F302" s="2" t="s">
+        <v>1974</v>
       </c>
       <c r="G302" t="s">
-        <v>876</v>
+        <v>79</v>
       </c>
       <c r="H302" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I302">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J302">
         <v>0</v>
       </c>
       <c r="K302" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="L302" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="303" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="B303" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>14</v>
+        <v>741</v>
       </c>
       <c r="D303" t="s">
         <v>56</v>
       </c>
       <c r="E303" t="s">
-        <v>115</v>
+        <v>692</v>
       </c>
       <c r="F303" s="2">
-        <v>2799488000194</v>
+        <v>10962296000185</v>
       </c>
       <c r="G303" t="s">
-        <v>396</v>
+        <v>1105</v>
       </c>
       <c r="H303" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I303">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="J303">
         <v>0</v>
       </c>
       <c r="K303" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="L303" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="304" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="B304" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>185</v>
+        <v>602</v>
       </c>
       <c r="D304" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E304" t="s">
-        <v>1901</v>
+        <v>31</v>
       </c>
       <c r="F304" s="2">
-        <v>0</v>
+        <v>12607842000195</v>
       </c>
       <c r="G304" t="s">
-        <v>79</v>
+        <v>1109</v>
       </c>
       <c r="H304" t="s">
-        <v>52</v>
+        <v>335</v>
       </c>
       <c r="I304">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="J304">
         <v>0</v>
       </c>
       <c r="K304" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="L304" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="305" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="B305" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>741</v>
+        <v>1113</v>
       </c>
       <c r="D305" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E305" t="s">
-        <v>692</v>
+        <v>31</v>
       </c>
       <c r="F305" s="2">
-        <v>10962296000185</v>
+        <v>7981751000185</v>
       </c>
       <c r="G305" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="H305" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I305">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J305">
         <v>0</v>
       </c>
       <c r="K305" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="L305" t="s">
         <v>1886</v>
@@ -17827,116 +17908,116 @@
     </row>
     <row r="306" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="B306" t="s">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>602</v>
+        <v>174</v>
       </c>
       <c r="D306" t="s">
-        <v>225</v>
+        <v>56</v>
       </c>
       <c r="E306" t="s">
-        <v>31</v>
+        <v>653</v>
       </c>
       <c r="F306" s="2">
-        <v>12607842000195</v>
+        <v>12610079000151</v>
       </c>
       <c r="G306" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="H306" t="s">
-        <v>335</v>
+        <v>17</v>
       </c>
       <c r="I306">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="J306">
         <v>0</v>
       </c>
       <c r="K306" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="L306" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="307" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="B307" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>1113</v>
+        <v>37</v>
       </c>
       <c r="D307" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E307" t="s">
-        <v>31</v>
+        <v>1948</v>
       </c>
       <c r="F307" s="2">
-        <v>7981751000185</v>
+        <v>24144040001309</v>
       </c>
       <c r="G307" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="H307" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="I307">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J307">
         <v>0</v>
       </c>
       <c r="K307" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="L307" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="308" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B308" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="D308" t="s">
         <v>56</v>
       </c>
       <c r="E308" t="s">
-        <v>653</v>
+        <v>1948</v>
       </c>
       <c r="F308" s="2">
-        <v>12610079000151</v>
+        <v>24144040001309</v>
       </c>
       <c r="G308" t="s">
-        <v>1118</v>
+        <v>977</v>
       </c>
       <c r="H308" t="s">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c r="I308">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J308">
         <v>0</v>
       </c>
       <c r="K308" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="L308" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="309" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17944,37 +18025,37 @@
         <v>1120</v>
       </c>
       <c r="B309" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D309" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E309" t="s">
-        <v>1954</v>
+        <v>1948</v>
       </c>
       <c r="F309" s="2">
         <v>24144040001309</v>
       </c>
       <c r="G309" t="s">
-        <v>1122</v>
+        <v>242</v>
       </c>
       <c r="H309" t="s">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="I309">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J309">
         <v>0</v>
       </c>
       <c r="K309" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="L309" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="310" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17982,72 +18063,72 @@
         <v>1120</v>
       </c>
       <c r="B310" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="D310" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E310" t="s">
-        <v>1954</v>
+        <v>1948</v>
       </c>
       <c r="F310" s="2">
         <v>24144040001309</v>
       </c>
       <c r="G310" t="s">
-        <v>977</v>
+        <v>16</v>
       </c>
       <c r="H310" t="s">
-        <v>285</v>
+        <v>17</v>
       </c>
       <c r="I310">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J310">
         <v>0</v>
       </c>
       <c r="K310" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="L310" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="311" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
       <c r="B311" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D311" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E311" t="s">
-        <v>1954</v>
+        <v>1132</v>
       </c>
       <c r="F311" s="2">
-        <v>24144040001309</v>
+        <v>36377091000126</v>
       </c>
       <c r="G311" t="s">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="H311" t="s">
-        <v>243</v>
+        <v>375</v>
       </c>
       <c r="I311">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J311">
         <v>0</v>
       </c>
       <c r="K311" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="L311" t="s">
         <v>1886</v>
@@ -18055,154 +18136,154 @@
     </row>
     <row r="312" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>1120</v>
+        <v>1134</v>
       </c>
       <c r="B312" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>13</v>
+        <v>358</v>
       </c>
       <c r="D312" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E312" t="s">
-        <v>1954</v>
-      </c>
-      <c r="F312" s="2">
-        <v>24144040001309</v>
+        <v>78</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>1136</v>
       </c>
       <c r="G312" t="s">
-        <v>16</v>
+        <v>1137</v>
       </c>
       <c r="H312" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I312">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J312">
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="L312" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="313" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
       <c r="B313" t="s">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D313" t="s">
-        <v>56</v>
+        <v>379</v>
       </c>
       <c r="E313" t="s">
-        <v>1132</v>
+        <v>1901</v>
       </c>
       <c r="F313" s="2">
-        <v>36377091000126</v>
+        <v>10556018000209</v>
       </c>
       <c r="G313" t="s">
-        <v>374</v>
+        <v>663</v>
       </c>
       <c r="H313" t="s">
-        <v>375</v>
+        <v>117</v>
       </c>
       <c r="I313">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J313">
         <v>0</v>
       </c>
       <c r="K313" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="L313" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="314" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="B314" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>358</v>
+        <v>137</v>
       </c>
       <c r="D314" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E314" t="s">
-        <v>78</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>1136</v>
+        <v>115</v>
+      </c>
+      <c r="F314" s="2">
+        <v>19700976000600</v>
       </c>
       <c r="G314" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="H314" t="s">
-        <v>39</v>
+        <v>243</v>
       </c>
       <c r="I314">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J314">
         <v>0</v>
       </c>
       <c r="K314" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="L314" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="315" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="B315" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>21</v>
+        <v>875</v>
       </c>
       <c r="D315" t="s">
-        <v>379</v>
+        <v>56</v>
       </c>
       <c r="E315" t="s">
-        <v>1901</v>
+        <v>115</v>
       </c>
       <c r="F315" s="2">
-        <v>10556018000209</v>
+        <v>19700976000600</v>
       </c>
       <c r="G315" t="s">
-        <v>663</v>
+        <v>1147</v>
       </c>
       <c r="H315" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="I315">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J315">
         <v>0</v>
       </c>
       <c r="K315" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="L315" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="316" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18210,13 +18291,13 @@
         <v>1142</v>
       </c>
       <c r="B316" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="D316" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="E316" t="s">
         <v>115</v>
@@ -18225,19 +18306,19 @@
         <v>19700976000600</v>
       </c>
       <c r="G316" t="s">
-        <v>1144</v>
+        <v>16</v>
       </c>
       <c r="H316" t="s">
-        <v>243</v>
+        <v>17</v>
       </c>
       <c r="I316">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J316">
         <v>0</v>
       </c>
       <c r="K316" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="L316" t="s">
         <v>1886</v>
@@ -18245,116 +18326,116 @@
     </row>
     <row r="317" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="B317" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>875</v>
+        <v>378</v>
       </c>
       <c r="D317" t="s">
         <v>56</v>
       </c>
       <c r="E317" t="s">
-        <v>115</v>
+        <v>692</v>
       </c>
       <c r="F317" s="2">
-        <v>19700976000600</v>
+        <v>796042000180</v>
       </c>
       <c r="G317" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="H317" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="I317">
-        <v>5</v>
-      </c>
-      <c r="J317">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J317" t="s">
+        <v>1895</v>
       </c>
       <c r="K317" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="L317" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="318" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="B318" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>46</v>
+        <v>1157</v>
       </c>
       <c r="D318" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="E318" t="s">
-        <v>115</v>
+        <v>1901</v>
       </c>
       <c r="F318" s="2">
-        <v>19700976000600</v>
+        <v>16404287000155</v>
       </c>
       <c r="G318" t="s">
-        <v>16</v>
+        <v>1159</v>
       </c>
       <c r="H318" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="I318">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J318">
         <v>0</v>
       </c>
       <c r="K318" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="L318" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="319" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B319" t="s">
-        <v>1152</v>
+        <v>1161</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>378</v>
+        <v>1095</v>
       </c>
       <c r="D319" t="s">
         <v>56</v>
       </c>
       <c r="E319" t="s">
-        <v>692</v>
+        <v>1901</v>
       </c>
       <c r="F319" s="2">
-        <v>796042000180</v>
+        <v>16404287000155</v>
       </c>
       <c r="G319" t="s">
-        <v>1153</v>
+        <v>1162</v>
       </c>
       <c r="H319" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="I319">
-        <v>2</v>
-      </c>
-      <c r="J319" t="s">
-        <v>1895</v>
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
       </c>
       <c r="K319" t="s">
-        <v>1154</v>
+        <v>1163</v>
       </c>
       <c r="L319" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="320" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18362,13 +18443,13 @@
         <v>1155</v>
       </c>
       <c r="B320" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>1157</v>
+        <v>126</v>
       </c>
       <c r="D320" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E320" t="s">
         <v>1901</v>
@@ -18377,22 +18458,22 @@
         <v>16404287000155</v>
       </c>
       <c r="G320" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="H320" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="I320">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J320">
         <v>0</v>
       </c>
       <c r="K320" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="L320" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="321" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18400,10 +18481,10 @@
         <v>1155</v>
       </c>
       <c r="B321" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>1095</v>
+        <v>349</v>
       </c>
       <c r="D321" t="s">
         <v>56</v>
@@ -18415,22 +18496,22 @@
         <v>16404287000155</v>
       </c>
       <c r="G321" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="H321" t="s">
-        <v>39</v>
+        <v>375</v>
       </c>
       <c r="I321">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J321">
         <v>0</v>
       </c>
       <c r="K321" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="L321" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="322" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18438,13 +18519,13 @@
         <v>1155</v>
       </c>
       <c r="B322" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="D322" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E322" t="s">
         <v>1901</v>
@@ -18453,22 +18534,22 @@
         <v>16404287000155</v>
       </c>
       <c r="G322" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="H322" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="I322">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="J322">
         <v>0</v>
       </c>
       <c r="K322" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="L322" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="323" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18476,13 +18557,13 @@
         <v>1155</v>
       </c>
       <c r="B323" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>349</v>
+        <v>875</v>
       </c>
       <c r="D323" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E323" t="s">
         <v>1901</v>
@@ -18491,19 +18572,19 @@
         <v>16404287000155</v>
       </c>
       <c r="G323" t="s">
-        <v>1168</v>
+        <v>588</v>
       </c>
       <c r="H323" t="s">
-        <v>375</v>
+        <v>17</v>
       </c>
       <c r="I323">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J323">
         <v>0</v>
       </c>
       <c r="K323" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="L323" t="s">
         <v>1886</v>
@@ -18514,13 +18595,13 @@
         <v>1155</v>
       </c>
       <c r="B324" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>46</v>
+        <v>494</v>
       </c>
       <c r="D324" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E324" t="s">
         <v>1901</v>
@@ -18529,22 +18610,22 @@
         <v>16404287000155</v>
       </c>
       <c r="G324" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="H324" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="I324">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J324">
         <v>0</v>
       </c>
       <c r="K324" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="L324" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="325" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18552,37 +18633,37 @@
         <v>1155</v>
       </c>
       <c r="B325" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>875</v>
+        <v>36</v>
       </c>
       <c r="D325" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="E325" t="s">
-        <v>1901</v>
+        <v>1158</v>
       </c>
       <c r="F325" s="2">
         <v>16404287000155</v>
       </c>
       <c r="G325" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="H325" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I325">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="J325">
         <v>0</v>
       </c>
       <c r="K325" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="L325" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="326" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18590,10 +18671,10 @@
         <v>1155</v>
       </c>
       <c r="B326" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>494</v>
+        <v>399</v>
       </c>
       <c r="D326" t="s">
         <v>56</v>
@@ -18605,22 +18686,22 @@
         <v>16404287000155</v>
       </c>
       <c r="G326" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="H326" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I326">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J326">
         <v>0</v>
       </c>
       <c r="K326" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="L326" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="327" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18628,34 +18709,34 @@
         <v>1155</v>
       </c>
       <c r="B327" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>36</v>
+        <v>875</v>
       </c>
       <c r="D327" t="s">
-        <v>185</v>
+        <v>476</v>
       </c>
       <c r="E327" t="s">
         <v>1158</v>
       </c>
       <c r="F327" s="2">
-        <v>16404287000155</v>
+        <v>16404287044870</v>
       </c>
       <c r="G327" t="s">
-        <v>613</v>
+        <v>865</v>
       </c>
       <c r="H327" t="s">
         <v>39</v>
       </c>
       <c r="I327">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="J327">
         <v>0</v>
       </c>
       <c r="K327" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="L327" t="s">
         <v>1887</v>
@@ -18663,113 +18744,113 @@
     </row>
     <row r="328" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
       <c r="B328" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>399</v>
+        <v>174</v>
       </c>
       <c r="D328" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E328" t="s">
-        <v>1901</v>
+        <v>495</v>
       </c>
       <c r="F328" s="2">
-        <v>16404287000155</v>
+        <v>1657682000172</v>
       </c>
       <c r="G328" t="s">
-        <v>1181</v>
+        <v>24</v>
       </c>
       <c r="H328" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I328">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J328">
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="L328" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="329" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>1155</v>
+        <v>1188</v>
       </c>
       <c r="B329" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>875</v>
+        <v>21</v>
       </c>
       <c r="D329" t="s">
-        <v>476</v>
+        <v>180</v>
       </c>
       <c r="E329" t="s">
-        <v>1158</v>
+        <v>31</v>
       </c>
       <c r="F329" s="2">
-        <v>16404287044870</v>
+        <v>54929021000115</v>
       </c>
       <c r="G329" t="s">
-        <v>865</v>
+        <v>1190</v>
       </c>
       <c r="H329" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I329">
-        <v>110</v>
-      </c>
-      <c r="J329">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="J329" t="s">
+        <v>1907</v>
       </c>
       <c r="K329" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="L329" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="330" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="B330" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="D330" t="s">
-        <v>22</v>
+        <v>359</v>
       </c>
       <c r="E330" t="s">
-        <v>495</v>
+        <v>31</v>
       </c>
       <c r="F330" s="2">
-        <v>1657682000172</v>
+        <v>47080619001199</v>
       </c>
       <c r="G330" t="s">
-        <v>24</v>
+        <v>796</v>
       </c>
       <c r="H330" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I330">
-        <v>1</v>
-      </c>
-      <c r="J330">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="J330" t="s">
+        <v>1907</v>
       </c>
       <c r="K330" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="L330" t="s">
         <v>1886</v>
@@ -18780,34 +18861,34 @@
         <v>1188</v>
       </c>
       <c r="B331" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D331" t="s">
-        <v>180</v>
+        <v>359</v>
       </c>
       <c r="E331" t="s">
         <v>31</v>
       </c>
       <c r="F331" s="2">
-        <v>54929021000115</v>
+        <v>47080619003302</v>
       </c>
       <c r="G331" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="H331" t="s">
         <v>17</v>
       </c>
       <c r="I331">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J331" t="s">
         <v>1907</v>
       </c>
       <c r="K331" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="L331" t="s">
         <v>1886</v>
@@ -18818,10 +18899,10 @@
         <v>1188</v>
       </c>
       <c r="B332" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>36</v>
+        <v>1198</v>
       </c>
       <c r="D332" t="s">
         <v>359</v>
@@ -18830,22 +18911,22 @@
         <v>31</v>
       </c>
       <c r="F332" s="2">
-        <v>47080619001199</v>
+        <v>5266880000166</v>
       </c>
       <c r="G332" t="s">
-        <v>796</v>
+        <v>1199</v>
       </c>
       <c r="H332" t="s">
         <v>17</v>
       </c>
       <c r="I332">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J332" t="s">
         <v>1907</v>
       </c>
       <c r="K332" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="L332" t="s">
         <v>1886</v>
@@ -18856,34 +18937,34 @@
         <v>1188</v>
       </c>
       <c r="B333" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="D333" t="s">
-        <v>359</v>
+        <v>47</v>
       </c>
       <c r="E333" t="s">
         <v>31</v>
       </c>
       <c r="F333" s="2">
-        <v>47080619003302</v>
+        <v>47080619003051</v>
       </c>
       <c r="G333" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="H333" t="s">
         <v>17</v>
       </c>
       <c r="I333">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="J333" t="s">
         <v>1907</v>
       </c>
       <c r="K333" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="L333" t="s">
         <v>1886</v>
@@ -18894,10 +18975,10 @@
         <v>1188</v>
       </c>
       <c r="B334" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>1198</v>
+        <v>36</v>
       </c>
       <c r="D334" t="s">
         <v>359</v>
@@ -18906,10 +18987,10 @@
         <v>31</v>
       </c>
       <c r="F334" s="2">
-        <v>5266880000166</v>
+        <v>54929021000115</v>
       </c>
       <c r="G334" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="H334" t="s">
         <v>17</v>
@@ -18921,7 +19002,7 @@
         <v>1907</v>
       </c>
       <c r="K334" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="L334" t="s">
         <v>1886</v>
@@ -18929,37 +19010,37 @@
     </row>
     <row r="335" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>1188</v>
+        <v>1207</v>
       </c>
       <c r="B335" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D335" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E335" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F335" s="2">
-        <v>47080619003051</v>
+        <v>19235340000120</v>
       </c>
       <c r="G335" t="s">
-        <v>1202</v>
+        <v>513</v>
       </c>
       <c r="H335" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I335">
-        <v>61</v>
-      </c>
-      <c r="J335" t="s">
-        <v>1907</v>
+        <v>8</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
       </c>
       <c r="K335" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="L335" t="s">
         <v>1886</v>
@@ -18967,37 +19048,37 @@
     </row>
     <row r="336" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>1188</v>
+        <v>1207</v>
       </c>
       <c r="B336" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>36</v>
+        <v>813</v>
       </c>
       <c r="D336" t="s">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="E336" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F336" s="2">
-        <v>54929021000115</v>
+        <v>19235340000120</v>
       </c>
       <c r="G336" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="H336" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I336">
-        <v>29</v>
-      </c>
-      <c r="J336" t="s">
-        <v>1907</v>
+        <v>9</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
       </c>
       <c r="K336" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="L336" t="s">
         <v>1886</v>
@@ -19008,13 +19089,13 @@
         <v>1207</v>
       </c>
       <c r="B337" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D337" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E337" t="s">
         <v>15</v>
@@ -19023,19 +19104,19 @@
         <v>19235340000120</v>
       </c>
       <c r="G337" t="s">
-        <v>513</v>
+        <v>1214</v>
       </c>
       <c r="H337" t="s">
         <v>25</v>
       </c>
       <c r="I337">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J337">
         <v>0</v>
       </c>
       <c r="K337" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="L337" t="s">
         <v>1886</v>
@@ -19046,13 +19127,13 @@
         <v>1207</v>
       </c>
       <c r="B338" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>813</v>
+        <v>168</v>
       </c>
       <c r="D338" t="s">
-        <v>77</v>
+        <v>476</v>
       </c>
       <c r="E338" t="s">
         <v>15</v>
@@ -19061,19 +19142,19 @@
         <v>19235340000120</v>
       </c>
       <c r="G338" t="s">
-        <v>1211</v>
+        <v>257</v>
       </c>
       <c r="H338" t="s">
         <v>25</v>
       </c>
       <c r="I338">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J338">
         <v>0</v>
       </c>
       <c r="K338" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="L338" t="s">
         <v>1886</v>
@@ -19081,28 +19162,28 @@
     </row>
     <row r="339" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>1207</v>
+        <v>1218</v>
       </c>
       <c r="B339" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>90</v>
+        <v>379</v>
       </c>
       <c r="D339" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E339" t="s">
         <v>15</v>
       </c>
-      <c r="F339" s="2">
-        <v>19235340000120</v>
+      <c r="F339" s="2" t="s">
+        <v>1982</v>
       </c>
       <c r="G339" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="H339" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="I339">
         <v>2</v>
@@ -19111,30 +19192,30 @@
         <v>0</v>
       </c>
       <c r="K339" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="L339" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="340" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>1207</v>
+        <v>1222</v>
       </c>
       <c r="B340" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>168</v>
+        <v>494</v>
       </c>
       <c r="D340" t="s">
-        <v>476</v>
+        <v>56</v>
       </c>
       <c r="E340" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="F340" s="2">
-        <v>19235340000120</v>
+        <v>41512627000109</v>
       </c>
       <c r="G340" t="s">
         <v>257</v>
@@ -19143,13 +19224,13 @@
         <v>25</v>
       </c>
       <c r="I340">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J340">
         <v>0</v>
       </c>
       <c r="K340" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="L340" t="s">
         <v>1886</v>
@@ -19157,37 +19238,37 @@
     </row>
     <row r="341" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="B341" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>379</v>
+        <v>1227</v>
       </c>
       <c r="D341" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E341" t="s">
-        <v>15</v>
-      </c>
-      <c r="F341" s="2">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="F341" s="2" t="s">
+        <v>1228</v>
       </c>
       <c r="G341" t="s">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="H341" t="s">
-        <v>233</v>
+        <v>52</v>
       </c>
       <c r="I341">
-        <v>2</v>
-      </c>
-      <c r="J341">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="J341" t="s">
+        <v>1230</v>
       </c>
       <c r="K341" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="L341" t="s">
         <v>1888</v>
@@ -19195,113 +19276,113 @@
     </row>
     <row r="342" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B342" t="s">
-        <v>1223</v>
+        <v>1232</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>494</v>
+        <v>1227</v>
       </c>
       <c r="D342" t="s">
         <v>56</v>
       </c>
       <c r="E342" t="s">
-        <v>115</v>
-      </c>
-      <c r="F342" s="2">
-        <v>41512627000109</v>
+        <v>63</v>
+      </c>
+      <c r="F342" s="2" t="s">
+        <v>1233</v>
       </c>
       <c r="G342" t="s">
-        <v>257</v>
+        <v>175</v>
       </c>
       <c r="H342" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="I342">
-        <v>4</v>
-      </c>
-      <c r="J342">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J342" t="s">
+        <v>1230</v>
       </c>
       <c r="K342" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
       <c r="L342" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="343" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="B343" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>1227</v>
+        <v>106</v>
       </c>
       <c r="D343" t="s">
         <v>56</v>
       </c>
       <c r="E343" t="s">
-        <v>63</v>
-      </c>
-      <c r="F343" s="2" t="s">
-        <v>1228</v>
+        <v>115</v>
+      </c>
+      <c r="F343" s="2">
+        <v>21038936000181</v>
       </c>
       <c r="G343" t="s">
-        <v>1229</v>
+        <v>16</v>
       </c>
       <c r="H343" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I343">
-        <v>12</v>
-      </c>
-      <c r="J343" t="s">
-        <v>1230</v>
+        <v>18</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
       </c>
       <c r="K343" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="L343" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="344" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
       <c r="B344" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>1227</v>
+        <v>737</v>
       </c>
       <c r="D344" t="s">
         <v>56</v>
       </c>
       <c r="E344" t="s">
-        <v>63</v>
-      </c>
-      <c r="F344" s="2" t="s">
-        <v>1233</v>
+        <v>115</v>
+      </c>
+      <c r="F344" s="2">
+        <v>17949900000859</v>
       </c>
       <c r="G344" t="s">
-        <v>175</v>
+        <v>1239</v>
       </c>
       <c r="H344" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I344">
-        <v>1</v>
-      </c>
-      <c r="J344" t="s">
-        <v>1230</v>
+        <v>4</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
       </c>
       <c r="K344" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="L344" t="s">
         <v>1887</v>
@@ -19309,13 +19390,13 @@
     </row>
     <row r="345" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="B345" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="D345" t="s">
         <v>56</v>
@@ -19324,22 +19405,22 @@
         <v>115</v>
       </c>
       <c r="F345" s="2">
-        <v>21038936000181</v>
+        <v>1934441000123</v>
       </c>
       <c r="G345" t="s">
-        <v>16</v>
+        <v>1243</v>
       </c>
       <c r="H345" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I345">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J345">
         <v>0</v>
       </c>
       <c r="K345" t="s">
-        <v>1224</v>
+        <v>1244</v>
       </c>
       <c r="L345" t="s">
         <v>1886</v>
@@ -19347,13 +19428,13 @@
     </row>
     <row r="346" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B346" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>737</v>
+        <v>14</v>
       </c>
       <c r="D346" t="s">
         <v>56</v>
@@ -19361,61 +19442,61 @@
       <c r="E346" t="s">
         <v>115</v>
       </c>
-      <c r="F346" s="2">
-        <v>17949900000859</v>
+      <c r="F346" s="2" t="s">
+        <v>1975</v>
       </c>
       <c r="G346" t="s">
-        <v>1239</v>
+        <v>764</v>
       </c>
       <c r="H346" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I346">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J346">
         <v>0</v>
       </c>
       <c r="K346" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="L346" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="347" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B347" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>37</v>
+        <v>472</v>
       </c>
       <c r="D347" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E347" t="s">
-        <v>115</v>
+        <v>1250</v>
       </c>
       <c r="F347" s="2">
-        <v>1934441000123</v>
+        <v>39232481000287</v>
       </c>
       <c r="G347" t="s">
-        <v>1243</v>
+        <v>457</v>
       </c>
       <c r="H347" t="s">
         <v>25</v>
       </c>
       <c r="I347">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J347">
         <v>0</v>
       </c>
       <c r="K347" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="L347" t="s">
         <v>1886</v>
@@ -19423,113 +19504,113 @@
     </row>
     <row r="348" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B348" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>14</v>
+        <v>317</v>
       </c>
       <c r="D348" t="s">
-        <v>56</v>
+        <v>379</v>
       </c>
       <c r="E348" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="F348" s="2">
-        <v>0</v>
+        <v>54470679000101</v>
       </c>
       <c r="G348" t="s">
-        <v>764</v>
+        <v>1254</v>
       </c>
       <c r="H348" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I348">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J348">
         <v>0</v>
       </c>
       <c r="K348" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="L348" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="349" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B349" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>472</v>
+        <v>143</v>
       </c>
       <c r="D349" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E349" t="s">
-        <v>1250</v>
+        <v>31</v>
       </c>
       <c r="F349" s="2">
-        <v>39232481000287</v>
+        <v>12229415000110</v>
       </c>
       <c r="G349" t="s">
-        <v>457</v>
+        <v>1258</v>
       </c>
       <c r="H349" t="s">
-        <v>25</v>
+        <v>335</v>
       </c>
       <c r="I349">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J349">
         <v>0</v>
       </c>
       <c r="K349" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="L349" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="350" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="B350" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="D350" t="s">
-        <v>379</v>
+        <v>185</v>
       </c>
       <c r="E350" t="s">
         <v>31</v>
       </c>
       <c r="F350" s="2">
-        <v>54470679000101</v>
+        <v>12229415001001</v>
       </c>
       <c r="G350" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
       <c r="H350" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I350">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="J350">
         <v>0</v>
       </c>
       <c r="K350" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="L350" t="s">
         <v>1886</v>
@@ -19537,28 +19618,28 @@
     </row>
     <row r="351" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B351" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>143</v>
+        <v>624</v>
       </c>
       <c r="D351" t="s">
-        <v>225</v>
+        <v>29</v>
       </c>
       <c r="E351" t="s">
         <v>31</v>
       </c>
       <c r="F351" s="2">
-        <v>12229415000110</v>
+        <v>61231478000206</v>
       </c>
       <c r="G351" t="s">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="H351" t="s">
-        <v>335</v>
+        <v>52</v>
       </c>
       <c r="I351">
         <v>30</v>
@@ -19567,45 +19648,45 @@
         <v>0</v>
       </c>
       <c r="K351" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="L351" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>1256</v>
+        <v>1267</v>
       </c>
       <c r="B352" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>378</v>
+        <v>494</v>
       </c>
       <c r="D352" t="s">
-        <v>185</v>
+        <v>359</v>
       </c>
       <c r="E352" t="s">
         <v>31</v>
       </c>
       <c r="F352" s="2">
-        <v>12229415001001</v>
+        <v>47063128000168</v>
       </c>
       <c r="G352" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="H352" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I352">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="J352">
         <v>0</v>
       </c>
       <c r="K352" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="L352" t="s">
         <v>1886</v>
@@ -19613,75 +19694,75 @@
     </row>
     <row r="353" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="B353" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>624</v>
+        <v>174</v>
       </c>
       <c r="D353" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E353" t="s">
         <v>31</v>
       </c>
       <c r="F353" s="2">
-        <v>61231478000206</v>
+        <v>5938884000143</v>
       </c>
       <c r="G353" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="H353" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I353">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="J353">
         <v>0</v>
       </c>
       <c r="K353" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="L353" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="354" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="B354" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>494</v>
+        <v>1277</v>
       </c>
       <c r="D354" t="s">
-        <v>359</v>
+        <v>56</v>
       </c>
       <c r="E354" t="s">
         <v>31</v>
       </c>
-      <c r="F354" s="2">
-        <v>47063128000168</v>
+      <c r="F354" s="2" t="s">
+        <v>1278</v>
       </c>
       <c r="G354" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
       <c r="H354" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I354">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="J354">
         <v>0</v>
       </c>
       <c r="K354" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="L354" t="s">
         <v>1886</v>
@@ -19689,341 +19770,341 @@
     </row>
     <row r="355" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>1271</v>
+        <v>1245</v>
       </c>
       <c r="B355" t="s">
-        <v>1272</v>
+        <v>1281</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>174</v>
+        <v>490</v>
       </c>
       <c r="D355" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="E355" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F355" s="2">
-        <v>5938884000143</v>
+        <v>75703256000164</v>
       </c>
       <c r="G355" t="s">
-        <v>1273</v>
+        <v>764</v>
       </c>
       <c r="H355" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I355">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="J355">
         <v>0</v>
       </c>
       <c r="K355" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="L355" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="356" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="B356" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>1277</v>
+        <v>494</v>
       </c>
       <c r="D356" t="s">
         <v>56</v>
       </c>
       <c r="E356" t="s">
-        <v>31</v>
-      </c>
-      <c r="F356" s="2" t="s">
-        <v>1278</v>
+        <v>1285</v>
+      </c>
+      <c r="F356" s="2">
+        <v>30820959000134</v>
       </c>
       <c r="G356" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
       <c r="H356" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="I356">
-        <v>4</v>
-      </c>
-      <c r="J356">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="J356" t="s">
+        <v>1287</v>
       </c>
       <c r="K356" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="L356" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="357" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>1245</v>
+        <v>1283</v>
       </c>
       <c r="B357" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>490</v>
+        <v>712</v>
       </c>
       <c r="D357" t="s">
         <v>56</v>
       </c>
       <c r="E357" t="s">
-        <v>115</v>
+        <v>1285</v>
       </c>
       <c r="F357" s="2">
-        <v>75703256000164</v>
+        <v>30820959000134</v>
       </c>
       <c r="G357" t="s">
-        <v>764</v>
+        <v>1908</v>
       </c>
       <c r="H357" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="I357">
-        <v>26</v>
-      </c>
-      <c r="J357">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J357" t="s">
+        <v>1287</v>
       </c>
       <c r="K357" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="L357" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="358" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="B358" t="s">
-        <v>1284</v>
+        <v>1909</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>494</v>
+        <v>353</v>
       </c>
       <c r="D358" t="s">
         <v>56</v>
       </c>
       <c r="E358" t="s">
-        <v>1285</v>
+        <v>15</v>
       </c>
       <c r="F358" s="2">
-        <v>30820959000134</v>
+        <v>14134894000117</v>
       </c>
       <c r="G358" t="s">
-        <v>1286</v>
+        <v>916</v>
       </c>
       <c r="H358" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="I358">
-        <v>8</v>
-      </c>
-      <c r="J358" t="s">
-        <v>1287</v>
+        <v>2</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
       </c>
       <c r="K358" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="L358" t="s">
-        <v>1887</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>1283</v>
+        <v>1294</v>
       </c>
       <c r="B359" t="s">
-        <v>1289</v>
+        <v>1880</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>712</v>
+        <v>929</v>
       </c>
       <c r="D359" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E359" t="s">
-        <v>1285</v>
+        <v>31</v>
       </c>
       <c r="F359" s="2">
-        <v>30820959000134</v>
+        <v>68316801002571</v>
       </c>
       <c r="G359" t="s">
-        <v>1908</v>
+        <v>1296</v>
       </c>
       <c r="H359" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I359">
-        <v>3</v>
-      </c>
-      <c r="J359" t="s">
-        <v>1287</v>
+        <v>21</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
       </c>
       <c r="K359" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="L359" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B360" t="s">
-        <v>1909</v>
+        <v>1298</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>353</v>
+        <v>929</v>
       </c>
       <c r="D360" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E360" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F360" s="2">
-        <v>14134894000117</v>
+        <v>68316801000102</v>
       </c>
       <c r="G360" t="s">
-        <v>916</v>
+        <v>1299</v>
       </c>
       <c r="H360" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="I360">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="J360">
         <v>0</v>
       </c>
       <c r="K360" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="L360" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
       <c r="B361" t="s">
-        <v>1880</v>
+        <v>1302</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>929</v>
+        <v>372</v>
       </c>
       <c r="D361" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="E361" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F361" s="2">
-        <v>68316801002571</v>
+        <v>32681371003350</v>
       </c>
       <c r="G361" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="H361" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I361">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J361">
         <v>0</v>
       </c>
       <c r="K361" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="L361" t="s">
         <v>1886</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>1294</v>
+        <v>1305</v>
       </c>
       <c r="B362" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>929</v>
+        <v>13</v>
       </c>
       <c r="D362" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="E362" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="F362" s="2">
-        <v>68316801000102</v>
+        <v>1105558000102</v>
       </c>
       <c r="G362" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="H362" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I362">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="J362">
         <v>0</v>
       </c>
       <c r="K362" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="L362" t="s">
         <v>1886</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="B363" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="D363" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E363" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="F363" s="2">
-        <v>32681371003350</v>
+        <v>1105558000102</v>
       </c>
       <c r="G363" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="H363" t="s">
         <v>25</v>
       </c>
       <c r="I363">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J363">
         <v>0</v>
       </c>
       <c r="K363" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="L363" t="s">
         <v>1886</v>
@@ -20031,158 +20112,82 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="B364" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>13</v>
+        <v>712</v>
       </c>
       <c r="D364" t="s">
-        <v>306</v>
+        <v>56</v>
       </c>
       <c r="E364" t="s">
-        <v>78</v>
-      </c>
-      <c r="F364">
-        <v>1105558000102</v>
+        <v>31</v>
+      </c>
+      <c r="F364" s="2" t="s">
+        <v>1314</v>
       </c>
       <c r="G364" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="H364" t="s">
-        <v>25</v>
+        <v>973</v>
       </c>
       <c r="I364">
-        <v>106</v>
-      </c>
-      <c r="J364">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="J364" t="s">
+        <v>1316</v>
       </c>
       <c r="K364" t="s">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="L364" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="B365" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>77</v>
+        <v>1944</v>
       </c>
       <c r="D365" t="s">
         <v>30</v>
       </c>
       <c r="E365" t="s">
-        <v>78</v>
-      </c>
-      <c r="F365">
-        <v>1105558000102</v>
+        <v>15</v>
+      </c>
+      <c r="F365" s="2" t="s">
+        <v>1320</v>
       </c>
       <c r="G365" t="s">
-        <v>1307</v>
+        <v>16</v>
       </c>
       <c r="H365" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I365">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="J365">
         <v>0</v>
       </c>
       <c r="K365" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
       <c r="L365" t="s">
         <v>1886</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A366" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C366" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="D366" t="s">
-        <v>56</v>
-      </c>
-      <c r="E366" t="s">
-        <v>31</v>
-      </c>
-      <c r="F366" t="s">
-        <v>1314</v>
-      </c>
-      <c r="G366" t="s">
-        <v>1315</v>
-      </c>
-      <c r="H366" t="s">
-        <v>973</v>
-      </c>
-      <c r="I366">
-        <v>4</v>
-      </c>
-      <c r="J366" t="s">
-        <v>1316</v>
-      </c>
-      <c r="K366" t="s">
-        <v>1317</v>
-      </c>
-      <c r="L366" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A367" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1319</v>
-      </c>
-      <c r="C367" s="3" t="s">
-        <v>1950</v>
-      </c>
-      <c r="D367" t="s">
-        <v>30</v>
-      </c>
-      <c r="E367" t="s">
-        <v>15</v>
-      </c>
-      <c r="F367" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G367" t="s">
-        <v>16</v>
-      </c>
-      <c r="H367" t="s">
-        <v>17</v>
-      </c>
-      <c r="I367">
-        <v>32</v>
-      </c>
-      <c r="J367">
-        <v>0</v>
-      </c>
-      <c r="K367" t="s">
-        <v>1321</v>
-      </c>
-      <c r="L367" t="s">
-        <v>1886</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L367" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L365" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -20315,6 +20320,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J311"/>
   <sheetFormatPr defaultColWidth="10.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -20362,7 +20368,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -20376,7 +20382,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -20395,7 +20401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -20409,7 +20415,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -20423,7 +20429,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -20437,7 +20443,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -20451,7 +20457,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -20465,7 +20471,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -20479,7 +20485,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -20493,7 +20499,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>85</v>
       </c>
@@ -20507,7 +20513,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -20521,7 +20527,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -20535,7 +20541,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -20549,7 +20555,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>110</v>
       </c>
@@ -20573,7 +20579,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -20587,7 +20593,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>129</v>
       </c>
@@ -20601,7 +20607,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -20615,7 +20621,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>136</v>
       </c>
@@ -20629,7 +20635,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>142</v>
       </c>
@@ -20643,7 +20649,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>146</v>
       </c>
@@ -20657,7 +20663,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>149</v>
       </c>
@@ -20671,7 +20677,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>152</v>
       </c>
@@ -20685,7 +20691,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>156</v>
       </c>
@@ -20699,7 +20705,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>167</v>
       </c>
@@ -20713,7 +20719,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>173</v>
       </c>
@@ -20727,7 +20733,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>178</v>
       </c>
@@ -20741,7 +20747,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>183</v>
       </c>
@@ -20755,7 +20761,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>188</v>
       </c>
@@ -20769,7 +20775,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>192</v>
       </c>
@@ -20783,7 +20789,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -20797,7 +20803,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>201</v>
       </c>
@@ -20811,7 +20817,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>205</v>
       </c>
@@ -20825,7 +20831,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>208</v>
       </c>
@@ -20857,7 +20863,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>211</v>
       </c>
@@ -20877,7 +20883,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>215</v>
       </c>
@@ -20897,7 +20903,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>218</v>
       </c>
@@ -20917,7 +20923,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>221</v>
       </c>
@@ -20937,7 +20943,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>224</v>
       </c>
@@ -20951,7 +20957,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>228</v>
       </c>
@@ -20971,7 +20977,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>231</v>
       </c>
@@ -20991,7 +20997,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>235</v>
       </c>
@@ -21011,7 +21017,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>238</v>
       </c>
@@ -21031,7 +21037,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>245</v>
       </c>
@@ -21051,7 +21057,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>247</v>
       </c>
@@ -21071,7 +21077,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>250</v>
       </c>
@@ -21091,7 +21097,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>253</v>
       </c>
@@ -21111,7 +21117,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>256</v>
       </c>
@@ -21131,7 +21137,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>259</v>
       </c>
@@ -21151,7 +21157,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>267</v>
       </c>
@@ -21183,7 +21189,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>272</v>
       </c>
@@ -21194,7 +21200,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>274</v>
       </c>
@@ -21205,7 +21211,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>278</v>
       </c>
@@ -21219,7 +21225,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>281</v>
       </c>
@@ -21230,7 +21236,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>283</v>
       </c>
@@ -21244,7 +21250,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>287</v>
       </c>
@@ -21255,7 +21261,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>290</v>
       </c>
@@ -21272,7 +21278,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>293</v>
       </c>
@@ -21283,7 +21289,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>296</v>
       </c>
@@ -21294,7 +21300,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>298</v>
       </c>
@@ -21305,7 +21311,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>301</v>
       </c>
@@ -21316,7 +21322,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>304</v>
       </c>
@@ -21327,7 +21333,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>309</v>
       </c>
@@ -21338,7 +21344,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>312</v>
       </c>
@@ -21349,7 +21355,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>316</v>
       </c>
@@ -21363,7 +21369,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>321</v>
       </c>
@@ -21377,7 +21383,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>328</v>
       </c>
@@ -21391,7 +21397,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>331</v>
       </c>
@@ -21405,7 +21411,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>334</v>
       </c>
@@ -21419,7 +21425,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>338</v>
       </c>
@@ -21430,7 +21436,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>341</v>
       </c>
@@ -21441,7 +21447,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>348</v>
       </c>
@@ -21452,7 +21458,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>352</v>
       </c>
@@ -21463,7 +21469,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>357</v>
       </c>
@@ -21479,7 +21485,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>371</v>
       </c>
@@ -21493,7 +21499,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>377</v>
       </c>
@@ -21507,7 +21513,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>382</v>
       </c>
@@ -21521,7 +21527,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>387</v>
       </c>
@@ -21535,7 +21541,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>391</v>
       </c>
@@ -21549,7 +21555,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>395</v>
       </c>
@@ -21563,7 +21569,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>398</v>
       </c>
@@ -21577,7 +21583,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>402</v>
       </c>
@@ -21591,7 +21597,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>404</v>
       </c>
@@ -21605,7 +21611,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>414</v>
       </c>
@@ -21619,7 +21625,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>417</v>
       </c>
@@ -21633,7 +21639,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>420</v>
       </c>
@@ -21647,7 +21653,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>423</v>
       </c>
@@ -21661,7 +21667,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>426</v>
       </c>
@@ -21675,7 +21681,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>429</v>
       </c>
@@ -21689,7 +21695,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>432</v>
       </c>
@@ -21703,7 +21709,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>435</v>
       </c>
@@ -21717,7 +21723,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>438</v>
       </c>
@@ -21731,7 +21737,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>441</v>
       </c>
@@ -21745,7 +21751,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>444</v>
       </c>
@@ -21759,7 +21765,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>447</v>
       </c>
@@ -21773,7 +21779,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>450</v>
       </c>
@@ -21787,7 +21793,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>453</v>
       </c>
@@ -21801,7 +21807,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>456</v>
       </c>
@@ -21815,7 +21821,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>459</v>
       </c>
@@ -21829,7 +21835,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>462</v>
       </c>
@@ -21843,7 +21849,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>464</v>
       </c>
@@ -21857,7 +21863,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>467</v>
       </c>
@@ -21871,7 +21877,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>471</v>
       </c>
@@ -21890,7 +21896,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>480</v>
       </c>
@@ -21904,7 +21910,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>489</v>
       </c>
@@ -21918,7 +21924,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>493</v>
       </c>
@@ -21932,7 +21938,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>506</v>
       </c>
@@ -21946,7 +21952,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>509</v>
       </c>
@@ -21960,7 +21966,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>512</v>
       </c>
@@ -21974,7 +21980,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>523</v>
       </c>
@@ -21988,7 +21994,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>527</v>
       </c>
@@ -21999,7 +22005,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>531</v>
       </c>
@@ -22015,7 +22021,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>542</v>
       </c>
@@ -22029,7 +22035,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>546</v>
       </c>
@@ -22040,7 +22046,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>563</v>
       </c>
@@ -22054,7 +22060,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>566</v>
       </c>
@@ -22068,7 +22074,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>570</v>
       </c>
@@ -22079,7 +22085,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>575</v>
       </c>
@@ -22093,7 +22099,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>578</v>
       </c>
@@ -22107,7 +22113,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>586</v>
       </c>
@@ -22121,7 +22127,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>590</v>
       </c>
@@ -22135,7 +22141,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>594</v>
       </c>
@@ -22149,7 +22155,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>598</v>
       </c>
@@ -22160,7 +22166,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>601</v>
       </c>
@@ -22174,7 +22180,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>610</v>
       </c>
@@ -22188,7 +22194,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>612</v>
       </c>
@@ -22202,7 +22208,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>615</v>
       </c>
@@ -22221,7 +22227,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>623</v>
       </c>
@@ -22235,7 +22241,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>627</v>
       </c>
@@ -22254,7 +22260,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>644</v>
       </c>
@@ -22268,7 +22274,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>647</v>
       </c>
@@ -22282,7 +22288,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>652</v>
       </c>
@@ -22296,7 +22302,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>656</v>
       </c>
@@ -22310,7 +22316,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>661</v>
       </c>
@@ -22324,7 +22330,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>666</v>
       </c>
@@ -22338,7 +22344,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>679</v>
       </c>
@@ -22377,7 +22383,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>722</v>
       </c>
@@ -22391,7 +22397,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>724</v>
       </c>
@@ -22405,7 +22411,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>727</v>
       </c>
@@ -22419,7 +22425,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>730</v>
       </c>
@@ -22433,7 +22439,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>734</v>
       </c>
@@ -22447,7 +22453,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>736</v>
       </c>
@@ -22461,7 +22467,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>740</v>
       </c>
@@ -22475,7 +22481,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>743</v>
       </c>
@@ -22489,7 +22495,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>745</v>
       </c>
@@ -22503,7 +22509,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>747</v>
       </c>
@@ -22517,7 +22523,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>748</v>
       </c>
@@ -22531,7 +22537,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>751</v>
       </c>
@@ -22545,7 +22551,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>754</v>
       </c>
@@ -22564,7 +22570,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>763</v>
       </c>
@@ -22578,7 +22584,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>773</v>
       </c>
@@ -22592,7 +22598,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>777</v>
       </c>
@@ -22606,7 +22612,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>780</v>
       </c>
@@ -22620,7 +22626,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>783</v>
       </c>
@@ -22634,7 +22640,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>786</v>
       </c>
@@ -22648,7 +22654,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>789</v>
       </c>
@@ -22662,7 +22668,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>792</v>
       </c>
@@ -22676,7 +22682,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>795</v>
       </c>
@@ -22690,7 +22696,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>805</v>
       </c>
@@ -22709,7 +22715,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>812</v>
       </c>
@@ -22723,7 +22729,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>816</v>
       </c>
@@ -22737,7 +22743,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>820</v>
       </c>
@@ -22751,7 +22757,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>824</v>
       </c>
@@ -22765,7 +22771,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>830</v>
       </c>
@@ -22779,7 +22785,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>834</v>
       </c>
@@ -22790,7 +22796,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>836</v>
       </c>
@@ -22801,7 +22807,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>839</v>
       </c>
@@ -22812,7 +22818,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>842</v>
       </c>
@@ -22823,7 +22829,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>845</v>
       </c>
@@ -22834,7 +22840,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>848</v>
       </c>
@@ -22845,7 +22851,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>851</v>
       </c>
@@ -22856,7 +22862,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>854</v>
       </c>
@@ -22867,7 +22873,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>857</v>
       </c>
@@ -22878,7 +22884,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>859</v>
       </c>
@@ -22889,7 +22895,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>862</v>
       </c>
@@ -22900,7 +22906,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>864</v>
       </c>
@@ -22911,7 +22917,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>867</v>
       </c>
@@ -22922,7 +22928,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>874</v>
       </c>
@@ -22936,7 +22942,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>886</v>
       </c>
@@ -22955,7 +22961,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>896</v>
       </c>
@@ -22969,7 +22975,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>898</v>
       </c>
@@ -22988,7 +22994,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>904</v>
       </c>
@@ -23012,7 +23018,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>915</v>
       </c>
@@ -23031,7 +23037,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>921</v>
       </c>
@@ -23045,7 +23051,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>925</v>
       </c>
@@ -23059,7 +23065,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>928</v>
       </c>
@@ -23073,7 +23079,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>932</v>
       </c>
@@ -23087,7 +23093,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>935</v>
       </c>
@@ -23101,7 +23107,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>939</v>
       </c>
@@ -23115,7 +23121,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>942</v>
       </c>
@@ -23129,7 +23135,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>950</v>
       </c>
@@ -23143,7 +23149,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>953</v>
       </c>
@@ -23157,7 +23163,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>957</v>
       </c>
@@ -23171,7 +23177,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>961</v>
       </c>
@@ -23179,7 +23185,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>965</v>
       </c>
@@ -23203,7 +23209,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>979</v>
       </c>
@@ -23217,7 +23223,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>982</v>
       </c>
@@ -23231,7 +23237,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>985</v>
       </c>
@@ -23245,7 +23251,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>988</v>
       </c>
@@ -23259,7 +23265,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>994</v>
       </c>
@@ -23273,7 +23279,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>996</v>
       </c>
@@ -23287,7 +23293,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>999</v>
       </c>
@@ -23301,7 +23307,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1001</v>
       </c>
@@ -23315,7 +23321,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1009</v>
       </c>
@@ -23329,7 +23335,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1011</v>
       </c>
@@ -23343,7 +23349,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1014</v>
       </c>
@@ -23357,7 +23363,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1017</v>
       </c>
@@ -23371,7 +23377,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1019</v>
       </c>
@@ -23385,7 +23391,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1023</v>
       </c>
@@ -23399,7 +23405,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1028</v>
       </c>
@@ -23413,7 +23419,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1031</v>
       </c>
@@ -23427,7 +23433,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1034</v>
       </c>
@@ -23441,7 +23447,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1036</v>
       </c>
@@ -23455,7 +23461,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1039</v>
       </c>
@@ -23469,7 +23475,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1043</v>
       </c>
@@ -23488,7 +23494,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1056</v>
       </c>
@@ -23502,7 +23508,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1058</v>
       </c>
@@ -23516,7 +23522,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1061</v>
       </c>
@@ -23530,7 +23536,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1064</v>
       </c>
@@ -23554,7 +23560,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1076</v>
       </c>
@@ -23568,7 +23574,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1081</v>
       </c>
@@ -23582,7 +23588,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1085</v>
       </c>
@@ -23596,7 +23602,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1091</v>
       </c>
@@ -23610,7 +23616,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1094</v>
       </c>
@@ -23629,7 +23635,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1104</v>
       </c>
@@ -23643,7 +23649,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1108</v>
       </c>
@@ -23657,7 +23663,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1112</v>
       </c>
@@ -23671,7 +23677,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1117</v>
       </c>
@@ -23695,7 +23701,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1126</v>
       </c>
@@ -23714,7 +23720,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1131</v>
       </c>
@@ -23736,7 +23742,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1140</v>
       </c>
@@ -23750,7 +23756,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1143</v>
       </c>
@@ -23764,7 +23770,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1146</v>
       </c>
@@ -23778,7 +23784,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1149</v>
       </c>
@@ -23792,7 +23798,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1152</v>
       </c>
@@ -23806,7 +23812,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1156</v>
       </c>
@@ -23820,7 +23826,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1161</v>
       </c>
@@ -23834,7 +23840,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1164</v>
       </c>
@@ -23848,7 +23854,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1167</v>
       </c>
@@ -23859,7 +23865,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1170</v>
       </c>
@@ -23873,7 +23879,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1173</v>
       </c>
@@ -23892,7 +23898,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1178</v>
       </c>
@@ -23906,7 +23912,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1180</v>
       </c>
@@ -23920,7 +23926,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1183</v>
       </c>
@@ -23934,7 +23940,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1186</v>
       </c>
@@ -23948,7 +23954,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1189</v>
       </c>
@@ -23959,7 +23965,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1192</v>
       </c>
@@ -23973,7 +23979,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1194</v>
       </c>
@@ -23987,7 +23993,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1197</v>
       </c>
@@ -24001,7 +24007,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1201</v>
       </c>
@@ -24015,7 +24021,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1204</v>
       </c>
@@ -24029,7 +24035,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1208</v>
       </c>
@@ -24043,7 +24049,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1210</v>
       </c>
@@ -24057,7 +24063,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1213</v>
       </c>
@@ -24071,7 +24077,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1216</v>
       </c>
@@ -24111,7 +24117,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1238</v>
       </c>
@@ -24125,7 +24131,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1242</v>
       </c>
@@ -24139,7 +24145,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>1249</v>
       </c>
@@ -24150,7 +24156,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1253</v>
       </c>
@@ -24164,7 +24170,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1257</v>
       </c>
@@ -24178,7 +24184,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1260</v>
       </c>
@@ -24192,7 +24198,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1264</v>
       </c>
@@ -24211,7 +24217,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1272</v>
       </c>
@@ -24230,7 +24236,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1281</v>
       </c>
@@ -24254,7 +24260,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1292</v>
       </c>
@@ -24268,7 +24274,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1295</v>
       </c>
@@ -24282,7 +24288,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1298</v>
       </c>
@@ -24296,7 +24302,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1302</v>
       </c>
@@ -24310,7 +24316,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1306</v>
       </c>
@@ -24324,7 +24330,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1310</v>
       </c>
@@ -24349,7 +24355,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J311" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:J311" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="1">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
